--- a/verification/model_verification_results_118_buses.xlsx
+++ b/verification/model_verification_results_118_buses.xlsx
@@ -554,10 +554,10 @@
         <v>11</v>
       </c>
       <c r="B9">
-        <v>154172.734375</v>
+        <v>154172.25</v>
       </c>
       <c r="C9">
-        <v>0.433578222990036</v>
+        <v>0.2941376268863678</v>
       </c>
     </row>
     <row r="10" spans="1:5">

--- a/verification/model_verification_results_118_buses.xlsx
+++ b/verification/model_verification_results_118_buses.xlsx
@@ -14,18 +14,81 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
-  <si>
-    <t>checkpoint_118_50_False_vr_vi_final.pt</t>
-  </si>
-  <si>
-    <t>checkpoint_118_50_True_vr_vi_final.pt</t>
-  </si>
-  <si>
-    <t>checkpoint_118_50_False_pg_vm_final.pt</t>
-  </si>
-  <si>
-    <t>checkpoint_118_50_True_pg_vm_final.pt</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="47">
+  <si>
+    <t>checkpoint_118_50_False_vr_vi_final.pt_0.00</t>
+  </si>
+  <si>
+    <t>checkpoint_118_50_False_vr_vi_final.pt_0.04</t>
+  </si>
+  <si>
+    <t>checkpoint_118_50_False_vr_vi_final.pt_0.08</t>
+  </si>
+  <si>
+    <t>checkpoint_118_50_False_vr_vi_final.pt_0.12</t>
+  </si>
+  <si>
+    <t>checkpoint_118_50_False_vr_vi_final.pt_0.16</t>
+  </si>
+  <si>
+    <t>checkpoint_118_50_False_vr_vi_final.pt_0.20</t>
+  </si>
+  <si>
+    <t>checkpoint_118_50_True_vr_vi_final.pt_0.00</t>
+  </si>
+  <si>
+    <t>checkpoint_118_50_True_vr_vi_final.pt_0.04</t>
+  </si>
+  <si>
+    <t>checkpoint_118_50_True_vr_vi_final.pt_0.08</t>
+  </si>
+  <si>
+    <t>checkpoint_118_50_True_vr_vi_final.pt_0.12</t>
+  </si>
+  <si>
+    <t>checkpoint_118_50_True_vr_vi_final.pt_0.16</t>
+  </si>
+  <si>
+    <t>checkpoint_118_50_True_vr_vi_final.pt_0.20</t>
+  </si>
+  <si>
+    <t>checkpoint_118_50_False_pg_vm_final.pt_0.00</t>
+  </si>
+  <si>
+    <t>checkpoint_118_50_False_pg_vm_final.pt_0.04</t>
+  </si>
+  <si>
+    <t>checkpoint_118_50_False_pg_vm_final.pt_0.08</t>
+  </si>
+  <si>
+    <t>checkpoint_118_50_False_pg_vm_final.pt_0.12</t>
+  </si>
+  <si>
+    <t>checkpoint_118_50_False_pg_vm_final.pt_0.16</t>
+  </si>
+  <si>
+    <t>checkpoint_118_50_False_pg_vm_final.pt_0.20</t>
+  </si>
+  <si>
+    <t>checkpoint_118_50_True_pg_vm_final.pt_0.00</t>
+  </si>
+  <si>
+    <t>checkpoint_118_50_True_pg_vm_final.pt_0.04</t>
+  </si>
+  <si>
+    <t>checkpoint_118_50_True_pg_vm_final.pt_0.08</t>
+  </si>
+  <si>
+    <t>checkpoint_118_50_True_pg_vm_final.pt_0.12</t>
+  </si>
+  <si>
+    <t>checkpoint_118_50_True_pg_vm_final.pt_0.16</t>
+  </si>
+  <si>
+    <t>checkpoint_118_50_True_pg_vm_final.pt_0.20</t>
+  </si>
+  <si>
+    <t>Metric</t>
   </si>
   <si>
     <t>Pg Up Max Violation</t>
@@ -40,6 +103,12 @@
     <t>Pg Down Avg Violation</t>
   </si>
   <si>
+    <t>Pg tot Max Violation</t>
+  </si>
+  <si>
+    <t>Pg tot Avg Violation</t>
+  </si>
+  <si>
     <t>Qg Up Max Violation</t>
   </si>
   <si>
@@ -52,10 +121,16 @@
     <t>Qg Down Avg Violation</t>
   </si>
   <si>
-    <t>Ibr Up Max Violation</t>
-  </si>
-  <si>
-    <t>Ibr Up Avg Violation</t>
+    <t>Qg tot Max Violation</t>
+  </si>
+  <si>
+    <t>Qg tot Avg Violation</t>
+  </si>
+  <si>
+    <t>Ibr tot Max Violation</t>
+  </si>
+  <si>
+    <t>Ibr tot Avg Violation</t>
   </si>
   <si>
     <t>Vm Up Max Violation</t>
@@ -70,10 +145,16 @@
     <t>Vm Down Avg Violation</t>
   </si>
   <si>
-    <t>Ibal Max Violation</t>
-  </si>
-  <si>
-    <t>Ibal Avg Violation</t>
+    <t>Vm tot Max Violation</t>
+  </si>
+  <si>
+    <t>Vm tot Avg Violation</t>
+  </si>
+  <si>
+    <t>Ibal tot Max Violation</t>
+  </si>
+  <si>
+    <t>Ibal tot Avg Violation</t>
   </si>
 </sst>
 </file>
@@ -431,10 +512,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E17"/>
+  <dimension ref="A1:Y23"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:25">
+      <c r="A1" s="1" t="s">
+        <v>24</v>
+      </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -447,229 +531,1399 @@
       <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" spans="1:5">
+      <c r="F1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="2" spans="1:25">
       <c r="A2" s="1" t="s">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="B2">
-        <v>2515426</v>
+        <v>100</v>
       </c>
       <c r="C2">
-        <v>1.412622690200806</v>
+        <v>97.08071708174958</v>
       </c>
       <c r="D2">
-        <v>56.09187698364258</v>
+        <v>94.26408350825439</v>
       </c>
       <c r="E2">
-        <v>3.215231895446777</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
+        <v>91.58459181936801</v>
+      </c>
+      <c r="F2">
+        <v>90.78353094684292</v>
+      </c>
+      <c r="G2">
+        <v>90.74588415498951</v>
+      </c>
+      <c r="H2">
+        <v>100</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>0</v>
+      </c>
+      <c r="K2">
+        <v>0</v>
+      </c>
+      <c r="L2">
+        <v>0</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>100</v>
+      </c>
+      <c r="O2">
+        <v>74.17841317948115</v>
+      </c>
+      <c r="P2">
+        <v>49.49022855982458</v>
+      </c>
+      <c r="Q2">
+        <v>32.16976813473167</v>
+      </c>
+      <c r="R2">
+        <v>23.15084910130469</v>
+      </c>
+      <c r="S2">
+        <v>20.47051528113071</v>
+      </c>
+      <c r="T2">
+        <v>100</v>
+      </c>
+      <c r="U2">
+        <v>93.8566359360982</v>
+      </c>
+      <c r="V2">
+        <v>90.22960417484221</v>
+      </c>
+      <c r="W2">
+        <v>86.89870191877442</v>
+      </c>
+      <c r="X2">
+        <v>83.9327339430528</v>
+      </c>
+      <c r="Y2">
+        <v>81.90906043986963</v>
+      </c>
+    </row>
+    <row r="3" spans="1:25">
       <c r="A3" s="1" t="s">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="B3">
-        <v>2123234.25</v>
+        <v>100</v>
       </c>
       <c r="C3">
-        <v>0.02478256449103355</v>
+        <v>99.42061332727532</v>
       </c>
       <c r="D3">
-        <v>18.53644752502441</v>
+        <v>98.86266062658564</v>
       </c>
       <c r="E3">
-        <v>0.4575319290161133</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
+        <v>98.337497604032</v>
+      </c>
+      <c r="F3">
+        <v>98.20212579555196</v>
+      </c>
+      <c r="G3">
+        <v>98.18726941206984</v>
+      </c>
+      <c r="H3">
+        <v>100</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>0</v>
+      </c>
+      <c r="K3">
+        <v>0</v>
+      </c>
+      <c r="L3">
+        <v>0</v>
+      </c>
+      <c r="M3">
+        <v>0</v>
+      </c>
+      <c r="N3">
+        <v>100</v>
+      </c>
+      <c r="O3">
+        <v>69.95696494881385</v>
+      </c>
+      <c r="P3">
+        <v>42.06544773142558</v>
+      </c>
+      <c r="Q3">
+        <v>22.16728492458746</v>
+      </c>
+      <c r="R3">
+        <v>13.50425608376204</v>
+      </c>
+      <c r="S3">
+        <v>11.40667834216298</v>
+      </c>
+      <c r="T3">
+        <v>100</v>
+      </c>
+      <c r="U3">
+        <v>92.64471042472677</v>
+      </c>
+      <c r="V3">
+        <v>84.34576458918724</v>
+      </c>
+      <c r="W3">
+        <v>79.2209891118538</v>
+      </c>
+      <c r="X3">
+        <v>74.53722575763378</v>
+      </c>
+      <c r="Y3">
+        <v>70.94965446091184</v>
+      </c>
+    </row>
+    <row r="4" spans="1:25">
       <c r="A4" s="1" t="s">
-        <v>6</v>
+        <v>27</v>
       </c>
       <c r="B4">
-        <v>2514877.25</v>
+        <v>100</v>
       </c>
       <c r="C4">
-        <v>6.177286148071289</v>
+        <v>97.08249027263875</v>
       </c>
       <c r="D4">
-        <v>44.31611251831055</v>
+        <v>94.26859592806655</v>
       </c>
       <c r="E4">
-        <v>0.8113818168640137</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
+        <v>91.56706991578879</v>
+      </c>
+      <c r="F4">
+        <v>90.88980405775607</v>
+      </c>
+      <c r="G4">
+        <v>90.86873677046495</v>
+      </c>
+      <c r="H4">
+        <v>100</v>
+      </c>
+      <c r="I4">
+        <v>63.9229067770905</v>
+      </c>
+      <c r="J4">
+        <v>39.93970005988486</v>
+      </c>
+      <c r="K4">
+        <v>25.84304928639227</v>
+      </c>
+      <c r="L4">
+        <v>16.15661327358997</v>
+      </c>
+      <c r="M4">
+        <v>11.30382416795916</v>
+      </c>
+      <c r="N4">
+        <v>100</v>
+      </c>
+      <c r="O4">
+        <v>66.82460796857725</v>
+      </c>
+      <c r="P4">
+        <v>34.09284207402154</v>
+      </c>
+      <c r="Q4">
+        <v>8.679315394082408</v>
+      </c>
+      <c r="R4">
+        <v>1.532833992018229</v>
+      </c>
+      <c r="S4">
+        <v>0.0275379403673629</v>
+      </c>
+      <c r="T4">
+        <v>100</v>
+      </c>
+      <c r="U4">
+        <v>67.29231621526677</v>
+      </c>
+      <c r="V4">
+        <v>48.72994345717242</v>
+      </c>
+      <c r="W4">
+        <v>27.05355510374859</v>
+      </c>
+      <c r="X4">
+        <v>9.434833227077283</v>
+      </c>
+      <c r="Y4">
+        <v>1.896174028921276</v>
+      </c>
+    </row>
+    <row r="5" spans="1:25">
       <c r="A5" s="1" t="s">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="B5">
-        <v>2122191.5</v>
+        <v>100</v>
       </c>
       <c r="C5">
-        <v>1.463666200637817</v>
+        <v>99.40993029997691</v>
       </c>
       <c r="D5">
-        <v>14.3839111328125</v>
+        <v>98.8422262786782</v>
       </c>
       <c r="E5">
-        <v>0.1366543173789978</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
+        <v>98.30168759602772</v>
+      </c>
+      <c r="F5">
+        <v>98.15737250166806</v>
+      </c>
+      <c r="G5">
+        <v>98.14288759448104</v>
+      </c>
+      <c r="H5">
+        <v>100</v>
+      </c>
+      <c r="I5">
+        <v>64.57509623459539</v>
+      </c>
+      <c r="J5">
+        <v>42.8852585269895</v>
+      </c>
+      <c r="K5">
+        <v>28.48496844152302</v>
+      </c>
+      <c r="L5">
+        <v>17.66013450152344</v>
+      </c>
+      <c r="M5">
+        <v>9.971380121147527</v>
+      </c>
+      <c r="N5">
+        <v>100</v>
+      </c>
+      <c r="O5">
+        <v>59.03538751236583</v>
+      </c>
+      <c r="P5">
+        <v>21.60625044903851</v>
+      </c>
+      <c r="Q5">
+        <v>3.520935492942432</v>
+      </c>
+      <c r="R5">
+        <v>0.5601919139200718</v>
+      </c>
+      <c r="S5">
+        <v>0.00698920600149333</v>
+      </c>
+      <c r="T5">
+        <v>100</v>
+      </c>
+      <c r="U5">
+        <v>66.28764919055384</v>
+      </c>
+      <c r="V5">
+        <v>42.57708231638868</v>
+      </c>
+      <c r="W5">
+        <v>21.3709430801243</v>
+      </c>
+      <c r="X5">
+        <v>8.818757381485343</v>
+      </c>
+      <c r="Y5">
+        <v>0.5563534275620854</v>
+      </c>
+    </row>
+    <row r="6" spans="1:25">
       <c r="A6" s="1" t="s">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="B6">
-        <v>679358.1875</v>
+        <v>100</v>
       </c>
       <c r="C6">
-        <v>4.519388198852539</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5">
+        <v>97.08071708174958</v>
+      </c>
+      <c r="D6">
+        <v>94.26408350825439</v>
+      </c>
+      <c r="E6">
+        <v>91.58459181936801</v>
+      </c>
+      <c r="F6">
+        <v>90.78353094684292</v>
+      </c>
+      <c r="G6">
+        <v>90.75787144721167</v>
+      </c>
+      <c r="H6">
+        <v>100</v>
+      </c>
+      <c r="I6">
+        <v>63.9229067770905</v>
+      </c>
+      <c r="J6">
+        <v>39.93970005988486</v>
+      </c>
+      <c r="K6">
+        <v>25.84304928639227</v>
+      </c>
+      <c r="L6">
+        <v>16.15661327358997</v>
+      </c>
+      <c r="M6">
+        <v>11.30382416795916</v>
+      </c>
+      <c r="N6">
+        <v>100</v>
+      </c>
+      <c r="O6">
+        <v>74.17841317948115</v>
+      </c>
+      <c r="P6">
+        <v>49.49022855982458</v>
+      </c>
+      <c r="Q6">
+        <v>32.16976813473167</v>
+      </c>
+      <c r="R6">
+        <v>23.15084910130469</v>
+      </c>
+      <c r="S6">
+        <v>20.47051528113071</v>
+      </c>
+      <c r="T6">
+        <v>100</v>
+      </c>
+      <c r="U6">
+        <v>93.8566359360982</v>
+      </c>
+      <c r="V6">
+        <v>90.22960417484221</v>
+      </c>
+      <c r="W6">
+        <v>86.89870191877442</v>
+      </c>
+      <c r="X6">
+        <v>83.9327339430528</v>
+      </c>
+      <c r="Y6">
+        <v>81.90906043986963</v>
+      </c>
+    </row>
+    <row r="7" spans="1:25">
       <c r="A7" s="1" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="B7">
-        <v>151561.234375</v>
+        <v>100</v>
       </c>
       <c r="C7">
-        <v>0.4037787318229675</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
+        <v>99.41525178456814</v>
+      </c>
+      <c r="D7">
+        <v>98.85243423654693</v>
+      </c>
+      <c r="E7">
+        <v>98.31958409827689</v>
+      </c>
+      <c r="F7">
+        <v>98.17973004650014</v>
+      </c>
+      <c r="G7">
+        <v>98.16506253125826</v>
+      </c>
+      <c r="H7">
+        <v>100</v>
+      </c>
+      <c r="I7">
+        <v>64.57348171294228</v>
+      </c>
+      <c r="J7">
+        <v>42.8841833157591</v>
+      </c>
+      <c r="K7">
+        <v>28.48425427168896</v>
+      </c>
+      <c r="L7">
+        <v>17.65969172991384</v>
+      </c>
+      <c r="M7">
+        <v>9.971130120558582</v>
+      </c>
+      <c r="N7">
+        <v>100</v>
+      </c>
+      <c r="O7">
+        <v>69.64495730342911</v>
+      </c>
+      <c r="P7">
+        <v>41.48096287286857</v>
+      </c>
+      <c r="Q7">
+        <v>21.63458674092214</v>
+      </c>
+      <c r="R7">
+        <v>13.13446451352029</v>
+      </c>
+      <c r="S7">
+        <v>11.08100666404445</v>
+      </c>
+      <c r="T7">
+        <v>100</v>
+      </c>
+      <c r="U7">
+        <v>92.58211146928646</v>
+      </c>
+      <c r="V7">
+        <v>84.24655237974736</v>
+      </c>
+      <c r="W7">
+        <v>79.08357579039593</v>
+      </c>
+      <c r="X7">
+        <v>74.381135819542</v>
+      </c>
+      <c r="Y7">
+        <v>70.78245002184174</v>
+      </c>
+    </row>
+    <row r="8" spans="1:25">
       <c r="A8" s="1" t="s">
-        <v>10</v>
+        <v>31</v>
       </c>
       <c r="B8">
-        <v>682124.4375</v>
+        <v>100</v>
       </c>
       <c r="C8">
-        <v>4.868465900421143</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5">
+        <v>68.2670316274659</v>
+      </c>
+      <c r="D8">
+        <v>37.84268362308156</v>
+      </c>
+      <c r="E8">
+        <v>8.048035532940494</v>
+      </c>
+      <c r="F8">
+        <v>0.8576987972351761</v>
+      </c>
+      <c r="G8">
+        <v>0.5290487265198803</v>
+      </c>
+      <c r="H8">
+        <v>100</v>
+      </c>
+      <c r="I8">
+        <v>52.26967527957643</v>
+      </c>
+      <c r="J8">
+        <v>36.54743874766725</v>
+      </c>
+      <c r="K8">
+        <v>27.00165214294803</v>
+      </c>
+      <c r="L8">
+        <v>19.72090597033521</v>
+      </c>
+      <c r="M8">
+        <v>13.39896159535288</v>
+      </c>
+    </row>
+    <row r="9" spans="1:25">
       <c r="A9" s="1" t="s">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="B9">
-        <v>154172.25</v>
+        <v>100</v>
       </c>
       <c r="C9">
-        <v>0.2941376268863678</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5">
+        <v>68.22034253094473</v>
+      </c>
+      <c r="D9">
+        <v>38.30574214435755</v>
+      </c>
+      <c r="E9">
+        <v>9.383507714160283</v>
+      </c>
+      <c r="F9">
+        <v>2.042658541992902</v>
+      </c>
+      <c r="G9">
+        <v>1.484162183203121</v>
+      </c>
+      <c r="H9">
+        <v>100</v>
+      </c>
+      <c r="I9">
+        <v>45.70170853761678</v>
+      </c>
+      <c r="J9">
+        <v>25.99130231005933</v>
+      </c>
+      <c r="K9">
+        <v>15.96374244826046</v>
+      </c>
+      <c r="L9">
+        <v>10.18210877776742</v>
+      </c>
+      <c r="M9">
+        <v>6.218497099543092</v>
+      </c>
+    </row>
+    <row r="10" spans="1:25">
       <c r="A10" s="1" t="s">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="B10">
-        <v>595.4048461914062</v>
+        <v>100</v>
       </c>
       <c r="C10">
-        <v>3.685477733612061</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5">
+        <v>68.45613376373582</v>
+      </c>
+      <c r="D10">
+        <v>38.20225348925477</v>
+      </c>
+      <c r="E10">
+        <v>8.479071178483782</v>
+      </c>
+      <c r="F10">
+        <v>0.871082945915571</v>
+      </c>
+      <c r="G10">
+        <v>0.6119943134626324</v>
+      </c>
+      <c r="H10">
+        <v>100</v>
+      </c>
+      <c r="I10">
+        <v>67.45768830005026</v>
+      </c>
+      <c r="J10">
+        <v>40.52636604696601</v>
+      </c>
+      <c r="K10">
+        <v>20.76225593843358</v>
+      </c>
+      <c r="L10">
+        <v>6.291282042672146</v>
+      </c>
+      <c r="M10">
+        <v>1.738313324316072</v>
+      </c>
+    </row>
+    <row r="11" spans="1:25">
       <c r="A11" s="1" t="s">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="B11">
-        <v>65.00618743896484</v>
+        <v>100</v>
       </c>
       <c r="C11">
-        <v>0.108115166425705</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5">
+        <v>68.24478501412364</v>
+      </c>
+      <c r="D11">
+        <v>38.51679296702105</v>
+      </c>
+      <c r="E11">
+        <v>9.880617964722044</v>
+      </c>
+      <c r="F11">
+        <v>2.278313223142147</v>
+      </c>
+      <c r="G11">
+        <v>1.618561412955744</v>
+      </c>
+      <c r="H11">
+        <v>100</v>
+      </c>
+      <c r="I11">
+        <v>45.412742702361</v>
+      </c>
+      <c r="J11">
+        <v>21.88228547157853</v>
+      </c>
+      <c r="K11">
+        <v>8.81655728846278</v>
+      </c>
+      <c r="L11">
+        <v>1.759423140537855</v>
+      </c>
+      <c r="M11">
+        <v>0.2338607476372556</v>
+      </c>
+    </row>
+    <row r="12" spans="1:25">
       <c r="A12" s="1" t="s">
-        <v>14</v>
+        <v>35</v>
       </c>
       <c r="B12">
-        <v>8.415285110473633</v>
+        <v>100</v>
       </c>
       <c r="C12">
-        <v>0.2827599048614502</v>
+        <v>68.45613376373582</v>
       </c>
       <c r="D12">
-        <v>1.394370317459106</v>
+        <v>38.20225348925477</v>
       </c>
       <c r="E12">
-        <v>0.01734089851379395</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5">
+        <v>8.479071178483782</v>
+      </c>
+      <c r="F12">
+        <v>0.871082945915571</v>
+      </c>
+      <c r="G12">
+        <v>0.6119943134626324</v>
+      </c>
+      <c r="H12">
+        <v>100</v>
+      </c>
+      <c r="I12">
+        <v>67.45768830005026</v>
+      </c>
+      <c r="J12">
+        <v>40.52636604696601</v>
+      </c>
+      <c r="K12">
+        <v>25.65247479766251</v>
+      </c>
+      <c r="L12">
+        <v>18.73552183817828</v>
+      </c>
+      <c r="M12">
+        <v>12.72946273139088</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25">
       <c r="A13" s="1" t="s">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="B13">
-        <v>3.770997762680054</v>
+        <v>100</v>
       </c>
       <c r="C13">
-        <v>0.1651065200567245</v>
+        <v>68.23266213368075</v>
       </c>
       <c r="D13">
-        <v>0.9205522537231445</v>
+        <v>38.41205608389068</v>
       </c>
       <c r="E13">
-        <v>0.003908303566277027</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5">
+        <v>9.633910603176869</v>
+      </c>
+      <c r="F13">
+        <v>2.161361583311725</v>
+      </c>
+      <c r="G13">
+        <v>1.551861324976318</v>
+      </c>
+      <c r="H13">
+        <v>100</v>
+      </c>
+      <c r="I13">
+        <v>45.60941128922716</v>
+      </c>
+      <c r="J13">
+        <v>24.67884277516628</v>
+      </c>
+      <c r="K13">
+        <v>13.68086188967295</v>
+      </c>
+      <c r="L13">
+        <v>7.491820136812126</v>
+      </c>
+      <c r="M13">
+        <v>4.306945695450507</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25">
       <c r="A14" s="1" t="s">
-        <v>16</v>
+        <v>37</v>
       </c>
       <c r="B14">
-        <v>7.41197395324707</v>
+        <v>100</v>
       </c>
       <c r="C14">
-        <v>0.5600539445877075</v>
+        <v>68.61504916208861</v>
       </c>
       <c r="D14">
-        <v>0.8946717977523804</v>
+        <v>39.63771841062741</v>
       </c>
       <c r="E14">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5">
+        <v>9.524192609606915</v>
+      </c>
+      <c r="F14">
+        <v>0.4095423711730822</v>
+      </c>
+      <c r="G14">
+        <v>0.01107840533053136</v>
+      </c>
+      <c r="H14">
+        <v>100</v>
+      </c>
+      <c r="I14">
+        <v>34.9596293579931</v>
+      </c>
+      <c r="J14">
+        <v>3.389381924725341</v>
+      </c>
+      <c r="K14">
+        <v>1.703532524367298</v>
+      </c>
+      <c r="L14">
+        <v>0.3393575550972595</v>
+      </c>
+      <c r="M14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25">
       <c r="A15" s="1" t="s">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="B15">
-        <v>0.827406644821167</v>
+        <v>100</v>
       </c>
       <c r="C15">
-        <v>0.2730548083782196</v>
+        <v>65.05505805050888</v>
       </c>
       <c r="D15">
-        <v>0.4135011732578278</v>
+        <v>32.68396721454123</v>
       </c>
       <c r="E15">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5">
+        <v>4.396581912180897</v>
+      </c>
+      <c r="F15">
+        <v>0.02854097013832294</v>
+      </c>
+      <c r="G15">
+        <v>0.0004624369916671608</v>
+      </c>
+      <c r="H15">
+        <v>100</v>
+      </c>
+      <c r="I15">
+        <v>16.54525732618782</v>
+      </c>
+      <c r="J15">
+        <v>1.291284008208946</v>
+      </c>
+      <c r="K15">
+        <v>0.3851268305836289</v>
+      </c>
+      <c r="L15">
+        <v>0.05852306042324259</v>
+      </c>
+      <c r="M15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:25">
       <c r="A16" s="1" t="s">
-        <v>18</v>
+        <v>39</v>
       </c>
       <c r="B16">
-        <v>4.456222534179688</v>
+        <v>100</v>
       </c>
       <c r="C16">
-        <v>1.403963685035706</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3">
+        <v>71.97868500896098</v>
+      </c>
+      <c r="D16">
+        <v>45.99677476233726</v>
+      </c>
+      <c r="E16">
+        <v>8.165904993111887</v>
+      </c>
+      <c r="F16">
+        <v>2.761963868483248</v>
+      </c>
+      <c r="G16">
+        <v>2.282996569953399</v>
+      </c>
+      <c r="H16">
+        <v>100</v>
+      </c>
+      <c r="I16">
+        <v>73.10039839981562</v>
+      </c>
+      <c r="J16">
+        <v>57.43285234512619</v>
+      </c>
+      <c r="K16">
+        <v>51.18048581729582</v>
+      </c>
+      <c r="L16">
+        <v>45.34051248703555</v>
+      </c>
+      <c r="M16">
+        <v>41.70809805245049</v>
+      </c>
+      <c r="N16">
+        <v>100</v>
+      </c>
+      <c r="O16">
+        <v>68.42075839541103</v>
+      </c>
+      <c r="P16">
+        <v>37.34071980271996</v>
+      </c>
+      <c r="Q16">
+        <v>13.69820579728939</v>
+      </c>
+      <c r="R16">
+        <v>2.932508385157989</v>
+      </c>
+      <c r="S16">
+        <v>0</v>
+      </c>
+      <c r="T16">
+        <v>100</v>
+      </c>
+      <c r="U16">
+        <v>72.59486009052286</v>
+      </c>
+      <c r="V16">
+        <v>50.40249516157637</v>
+      </c>
+      <c r="W16">
+        <v>29.42995273380574</v>
+      </c>
+      <c r="X16">
+        <v>10.78563662860183</v>
+      </c>
+      <c r="Y16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:25">
       <c r="A17" s="1" t="s">
-        <v>19</v>
+        <v>40</v>
       </c>
       <c r="B17">
-        <v>2.85697078704834</v>
+        <v>100</v>
       </c>
       <c r="C17">
-        <v>0.9387974739074707</v>
+        <v>76.00455513164393</v>
+      </c>
+      <c r="D17">
+        <v>39.03139130618764</v>
+      </c>
+      <c r="E17">
+        <v>14.50441585890808</v>
+      </c>
+      <c r="F17">
+        <v>7.349653310190075</v>
+      </c>
+      <c r="G17">
+        <v>4.106128644095335</v>
+      </c>
+      <c r="H17">
+        <v>100</v>
+      </c>
+      <c r="I17">
+        <v>74.41193269299417</v>
+      </c>
+      <c r="J17">
+        <v>58.70644783884934</v>
+      </c>
+      <c r="K17">
+        <v>44.5306507262169</v>
+      </c>
+      <c r="L17">
+        <v>32.01147396515803</v>
+      </c>
+      <c r="M17">
+        <v>23.58484698134584</v>
+      </c>
+      <c r="N17">
+        <v>100</v>
+      </c>
+      <c r="O17">
+        <v>67.37733532364706</v>
+      </c>
+      <c r="P17">
+        <v>35.77658450336362</v>
+      </c>
+      <c r="Q17">
+        <v>11.15990775762401</v>
+      </c>
+      <c r="R17">
+        <v>0.9210604732360059</v>
+      </c>
+      <c r="S17">
+        <v>0</v>
+      </c>
+      <c r="T17">
+        <v>100</v>
+      </c>
+      <c r="U17">
+        <v>53.9248635276161</v>
+      </c>
+      <c r="V17">
+        <v>26.53893891616757</v>
+      </c>
+      <c r="W17">
+        <v>11.22466432366339</v>
+      </c>
+      <c r="X17">
+        <v>2.758633228018589</v>
+      </c>
+      <c r="Y17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:25">
+      <c r="A18" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B18">
+        <v>100</v>
+      </c>
+      <c r="C18">
+        <v>60.7229157361331</v>
+      </c>
+      <c r="D18">
+        <v>27.97555158809081</v>
+      </c>
+      <c r="E18">
+        <v>15.25931360814973</v>
+      </c>
+      <c r="F18">
+        <v>4.593768393794482</v>
+      </c>
+      <c r="G18">
+        <v>0</v>
+      </c>
+      <c r="H18">
+        <v>100</v>
+      </c>
+      <c r="I18">
+        <v>70.48084578667711</v>
+      </c>
+      <c r="J18">
+        <v>43.00011617541635</v>
+      </c>
+      <c r="K18">
+        <v>0</v>
+      </c>
+      <c r="L18">
+        <v>0</v>
+      </c>
+      <c r="M18">
+        <v>0</v>
+      </c>
+      <c r="N18">
+        <v>100</v>
+      </c>
+      <c r="O18">
+        <v>57.78763288986668</v>
+      </c>
+      <c r="P18">
+        <v>18.78020794817624</v>
+      </c>
+      <c r="Q18">
+        <v>0</v>
+      </c>
+      <c r="R18">
+        <v>0</v>
+      </c>
+      <c r="S18">
+        <v>0</v>
+      </c>
+      <c r="T18">
+        <v>0</v>
+      </c>
+      <c r="U18">
+        <v>0</v>
+      </c>
+      <c r="V18">
+        <v>0</v>
+      </c>
+      <c r="W18">
+        <v>0</v>
+      </c>
+      <c r="X18">
+        <v>0</v>
+      </c>
+      <c r="Y18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:25">
+      <c r="A19" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B19">
+        <v>100</v>
+      </c>
+      <c r="C19">
+        <v>78.43526195351055</v>
+      </c>
+      <c r="D19">
+        <v>50.96690713157989</v>
+      </c>
+      <c r="E19">
+        <v>16.32535488543899</v>
+      </c>
+      <c r="F19">
+        <v>0.3804916538860575</v>
+      </c>
+      <c r="G19">
+        <v>0</v>
+      </c>
+      <c r="H19">
+        <v>100</v>
+      </c>
+      <c r="I19">
+        <v>13.23740358050935</v>
+      </c>
+      <c r="J19">
+        <v>6.416002550584768</v>
+      </c>
+      <c r="K19">
+        <v>0</v>
+      </c>
+      <c r="L19">
+        <v>0</v>
+      </c>
+      <c r="M19">
+        <v>0</v>
+      </c>
+      <c r="N19">
+        <v>100</v>
+      </c>
+      <c r="O19">
+        <v>49.06753113552977</v>
+      </c>
+      <c r="P19">
+        <v>4.324702749845449</v>
+      </c>
+      <c r="Q19">
+        <v>0</v>
+      </c>
+      <c r="R19">
+        <v>0</v>
+      </c>
+      <c r="S19">
+        <v>0</v>
+      </c>
+      <c r="T19">
+        <v>0</v>
+      </c>
+      <c r="U19">
+        <v>0</v>
+      </c>
+      <c r="V19">
+        <v>0</v>
+      </c>
+      <c r="W19">
+        <v>0</v>
+      </c>
+      <c r="X19">
+        <v>0</v>
+      </c>
+      <c r="Y19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:25">
+      <c r="A20" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B20">
+        <v>100</v>
+      </c>
+      <c r="C20">
+        <v>71.97868500896098</v>
+      </c>
+      <c r="D20">
+        <v>45.99677476233726</v>
+      </c>
+      <c r="E20">
+        <v>10.26805472841607</v>
+      </c>
+      <c r="F20">
+        <v>3.09116559816672</v>
+      </c>
+      <c r="G20">
+        <v>2.282996569953399</v>
+      </c>
+      <c r="H20">
+        <v>100</v>
+      </c>
+      <c r="I20">
+        <v>70.48084578667711</v>
+      </c>
+      <c r="J20">
+        <v>43.00011617541635</v>
+      </c>
+      <c r="K20">
+        <v>18.43305488908583</v>
+      </c>
+      <c r="L20">
+        <v>16.32974251859038</v>
+      </c>
+      <c r="M20">
+        <v>15.02149986353558</v>
+      </c>
+      <c r="N20">
+        <v>100</v>
+      </c>
+      <c r="O20">
+        <v>68.42075839541103</v>
+      </c>
+      <c r="P20">
+        <v>37.34071980271996</v>
+      </c>
+      <c r="Q20">
+        <v>13.69820579728939</v>
+      </c>
+      <c r="R20">
+        <v>2.932508385157989</v>
+      </c>
+      <c r="S20">
+        <v>0</v>
+      </c>
+      <c r="T20">
+        <v>100</v>
+      </c>
+      <c r="U20">
+        <v>72.59486009052286</v>
+      </c>
+      <c r="V20">
+        <v>50.40249516157637</v>
+      </c>
+      <c r="W20">
+        <v>29.42995273380574</v>
+      </c>
+      <c r="X20">
+        <v>10.78563662860183</v>
+      </c>
+      <c r="Y20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:25">
+      <c r="A21" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B21">
+        <v>100</v>
+      </c>
+      <c r="C21">
+        <v>77.23932907262585</v>
+      </c>
+      <c r="D21">
+        <v>45.09444779932792</v>
+      </c>
+      <c r="E21">
+        <v>15.42942584942032</v>
+      </c>
+      <c r="F21">
+        <v>3.809430500536067</v>
+      </c>
+      <c r="G21">
+        <v>2.02028083124552</v>
+      </c>
+      <c r="H21">
+        <v>100</v>
+      </c>
+      <c r="I21">
+        <v>42.14425218523644</v>
+      </c>
+      <c r="J21">
+        <v>31.12484699482849</v>
+      </c>
+      <c r="K21">
+        <v>21.04210152546269</v>
+      </c>
+      <c r="L21">
+        <v>15.12640561432428</v>
+      </c>
+      <c r="M21">
+        <v>11.14456529492854</v>
+      </c>
+      <c r="N21">
+        <v>100</v>
+      </c>
+      <c r="O21">
+        <v>62.55130915276234</v>
+      </c>
+      <c r="P21">
+        <v>27.48660859134573</v>
+      </c>
+      <c r="Q21">
+        <v>8.218417242667662</v>
+      </c>
+      <c r="R21">
+        <v>0.6782904876262205</v>
+      </c>
+      <c r="S21">
+        <v>0</v>
+      </c>
+      <c r="T21">
+        <v>100</v>
+      </c>
+      <c r="U21">
+        <v>53.9248635276161</v>
+      </c>
+      <c r="V21">
+        <v>26.53893891616757</v>
+      </c>
+      <c r="W21">
+        <v>11.22466432366339</v>
+      </c>
+      <c r="X21">
+        <v>2.758633228018589</v>
+      </c>
+      <c r="Y21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:25">
+      <c r="A22" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B22">
+        <v>100</v>
+      </c>
+      <c r="C22">
+        <v>93.12654178761444</v>
+      </c>
+      <c r="D22">
+        <v>87.29065898306889</v>
+      </c>
+      <c r="E22">
+        <v>83.03202550552105</v>
+      </c>
+      <c r="F22">
+        <v>80.93872746956058</v>
+      </c>
+      <c r="G22">
+        <v>80.01698397463683</v>
+      </c>
+      <c r="H22">
+        <v>100</v>
+      </c>
+      <c r="I22">
+        <v>99.00500531683059</v>
+      </c>
+      <c r="J22">
+        <v>98.20464837772704</v>
+      </c>
+      <c r="K22">
+        <v>97.5707762393108</v>
+      </c>
+      <c r="L22">
+        <v>97.12111915131804</v>
+      </c>
+      <c r="M22">
+        <v>96.87055256884388</v>
+      </c>
+    </row>
+    <row r="23" spans="1:25">
+      <c r="A23" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B23">
+        <v>100</v>
+      </c>
+      <c r="C23">
+        <v>91.530830337182</v>
+      </c>
+      <c r="D23">
+        <v>85.42968163711879</v>
+      </c>
+      <c r="E23">
+        <v>81.87477183407282</v>
+      </c>
+      <c r="F23">
+        <v>80.64101544569995</v>
+      </c>
+      <c r="G23">
+        <v>80.14352906683713</v>
+      </c>
+      <c r="H23">
+        <v>100</v>
+      </c>
+      <c r="I23">
+        <v>99.59048818998274</v>
+      </c>
+      <c r="J23">
+        <v>99.26513695524228</v>
+      </c>
+      <c r="K23">
+        <v>99.00585362585127</v>
+      </c>
+      <c r="L23">
+        <v>98.80802740217099</v>
+      </c>
+      <c r="M23">
+        <v>98.6953459302986</v>
       </c>
     </row>
   </sheetData>

--- a/verification/model_verification_results_118_buses.xlsx
+++ b/verification/model_verification_results_118_buses.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="53">
   <si>
     <t>checkpoint_118_50_False_vr_vi_final.pt_0.00</t>
   </si>
@@ -139,16 +139,34 @@
     <t>Vm Up Avg Violation</t>
   </si>
   <si>
+    <t>Vmg Up Max Violation</t>
+  </si>
+  <si>
+    <t>Vmg Up Avg Violation</t>
+  </si>
+  <si>
     <t>Vm Down Max Violation</t>
   </si>
   <si>
     <t>Vm Down Avg Violation</t>
   </si>
   <si>
+    <t>Vmg Down Max Violation</t>
+  </si>
+  <si>
+    <t>Vmg Down Avg Violation</t>
+  </si>
+  <si>
     <t>Vm tot Max Violation</t>
   </si>
   <si>
     <t>Vm tot Avg Violation</t>
+  </si>
+  <si>
+    <t>Vmg tot Max Violation</t>
+  </si>
+  <si>
+    <t>Vmg tot Avg Violation</t>
   </si>
   <si>
     <t>Ibal tot Max Violation</t>
@@ -512,7 +530,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Y23"/>
+  <dimension ref="A1:Y29"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:25">
@@ -600,22 +618,22 @@
         <v>100</v>
       </c>
       <c r="C2">
-        <v>97.08071708174958</v>
+        <v>99.61733143574618</v>
       </c>
       <c r="D2">
-        <v>94.26408350825439</v>
+        <v>99.21929569621042</v>
       </c>
       <c r="E2">
-        <v>91.58459181936801</v>
+        <v>98.68718566896206</v>
       </c>
       <c r="F2">
-        <v>90.78353094684292</v>
+        <v>98.66272892049972</v>
       </c>
       <c r="G2">
-        <v>90.74588415498951</v>
+        <v>98.63954865890871</v>
       </c>
       <c r="H2">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -636,37 +654,37 @@
         <v>100</v>
       </c>
       <c r="O2">
-        <v>74.17841317948115</v>
+        <v>76.86303066952948</v>
       </c>
       <c r="P2">
-        <v>49.49022855982458</v>
+        <v>54.27786445996389</v>
       </c>
       <c r="Q2">
-        <v>32.16976813473167</v>
+        <v>36.47793119306553</v>
       </c>
       <c r="R2">
-        <v>23.15084910130469</v>
+        <v>26.86390342193958</v>
       </c>
       <c r="S2">
-        <v>20.47051528113071</v>
+        <v>23.90676400428615</v>
       </c>
       <c r="T2">
         <v>100</v>
       </c>
       <c r="U2">
-        <v>93.8566359360982</v>
+        <v>95.93178191527458</v>
       </c>
       <c r="V2">
-        <v>90.22960417484221</v>
+        <v>92.56888002691697</v>
       </c>
       <c r="W2">
-        <v>86.89870191877442</v>
+        <v>89.21277741012054</v>
       </c>
       <c r="X2">
-        <v>83.9327339430528</v>
+        <v>86.20175692413177</v>
       </c>
       <c r="Y2">
-        <v>81.90906043986963</v>
+        <v>84.14062268722108</v>
       </c>
     </row>
     <row r="3" spans="1:25">
@@ -677,22 +695,22 @@
         <v>100</v>
       </c>
       <c r="C3">
-        <v>99.42061332727532</v>
+        <v>99.99509658663789</v>
       </c>
       <c r="D3">
-        <v>98.86266062658564</v>
+        <v>99.91764012314678</v>
       </c>
       <c r="E3">
-        <v>98.337497604032</v>
+        <v>99.78444320368817</v>
       </c>
       <c r="F3">
-        <v>98.20212579555196</v>
+        <v>99.73630116690009</v>
       </c>
       <c r="G3">
-        <v>98.18726941206984</v>
+        <v>99.71225198304393</v>
       </c>
       <c r="H3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -713,37 +731,37 @@
         <v>100</v>
       </c>
       <c r="O3">
-        <v>69.95696494881385</v>
+        <v>71.19148824739194</v>
       </c>
       <c r="P3">
-        <v>42.06544773142558</v>
+        <v>44.01931339549556</v>
       </c>
       <c r="Q3">
-        <v>22.16728492458746</v>
+        <v>24.60854116182523</v>
       </c>
       <c r="R3">
-        <v>13.50425608376204</v>
+        <v>15.90050217245484</v>
       </c>
       <c r="S3">
-        <v>11.40667834216298</v>
+        <v>13.50854579478409</v>
       </c>
       <c r="T3">
         <v>100</v>
       </c>
       <c r="U3">
-        <v>92.64471042472677</v>
+        <v>94.16991656064667</v>
       </c>
       <c r="V3">
-        <v>84.34576458918724</v>
+        <v>89.31895896217742</v>
       </c>
       <c r="W3">
-        <v>79.2209891118538</v>
+        <v>84.53463920402312</v>
       </c>
       <c r="X3">
-        <v>74.53722575763378</v>
+        <v>80.35014662634673</v>
       </c>
       <c r="Y3">
-        <v>70.94965446091184</v>
+        <v>77.47008688558064</v>
       </c>
     </row>
     <row r="4" spans="1:25">
@@ -754,73 +772,73 @@
         <v>100</v>
       </c>
       <c r="C4">
-        <v>97.08249027263875</v>
+        <v>99.92495980901941</v>
       </c>
       <c r="D4">
-        <v>94.26859592806655</v>
+        <v>99.92398801175949</v>
       </c>
       <c r="E4">
-        <v>91.56706991578879</v>
+        <v>99.7055641186537</v>
       </c>
       <c r="F4">
-        <v>90.88980405775607</v>
+        <v>99.67221153833576</v>
       </c>
       <c r="G4">
-        <v>90.86873677046495</v>
+        <v>99.64383007477046</v>
       </c>
       <c r="H4">
         <v>100</v>
       </c>
       <c r="I4">
-        <v>63.9229067770905</v>
+        <v>50.41963123863514</v>
       </c>
       <c r="J4">
-        <v>39.93970005988486</v>
+        <v>25.4086188313229</v>
       </c>
       <c r="K4">
-        <v>25.84304928639227</v>
+        <v>16.45881412865258</v>
       </c>
       <c r="L4">
-        <v>16.15661327358997</v>
+        <v>8.188443037126177</v>
       </c>
       <c r="M4">
-        <v>11.30382416795916</v>
+        <v>3.222028219426738</v>
       </c>
       <c r="N4">
         <v>100</v>
       </c>
       <c r="O4">
-        <v>66.82460796857725</v>
+        <v>67.66598141179935</v>
       </c>
       <c r="P4">
-        <v>34.09284207402154</v>
+        <v>34.31922353100933</v>
       </c>
       <c r="Q4">
-        <v>8.679315394082408</v>
+        <v>9.266275929755457</v>
       </c>
       <c r="R4">
-        <v>1.532833992018229</v>
+        <v>1.755218645801282</v>
       </c>
       <c r="S4">
-        <v>0.0275379403673629</v>
+        <v>0.03355261499920738</v>
       </c>
       <c r="T4">
         <v>100</v>
       </c>
       <c r="U4">
-        <v>67.29231621526677</v>
+        <v>68.18773844537272</v>
       </c>
       <c r="V4">
-        <v>48.72994345717242</v>
+        <v>48.11516307146195</v>
       </c>
       <c r="W4">
-        <v>27.05355510374859</v>
+        <v>28.26641616860171</v>
       </c>
       <c r="X4">
-        <v>9.434833227077283</v>
+        <v>10.00765540221346</v>
       </c>
       <c r="Y4">
-        <v>1.896174028921276</v>
+        <v>2.011296564461774</v>
       </c>
     </row>
     <row r="5" spans="1:25">
@@ -831,73 +849,73 @@
         <v>100</v>
       </c>
       <c r="C5">
-        <v>99.40993029997691</v>
+        <v>99.99051020961504</v>
       </c>
       <c r="D5">
-        <v>98.8422262786782</v>
+        <v>99.98594961252417</v>
       </c>
       <c r="E5">
-        <v>98.30168759602772</v>
+        <v>99.90036032465454</v>
       </c>
       <c r="F5">
-        <v>98.15737250166806</v>
+        <v>99.8336569066557</v>
       </c>
       <c r="G5">
-        <v>98.14288759448104</v>
+        <v>99.80857987004921</v>
       </c>
       <c r="H5">
         <v>100</v>
       </c>
       <c r="I5">
-        <v>64.57509623459539</v>
+        <v>60.89431410642364</v>
       </c>
       <c r="J5">
-        <v>42.8852585269895</v>
+        <v>29.55941288745796</v>
       </c>
       <c r="K5">
-        <v>28.48496844152302</v>
+        <v>15.4717800952286</v>
       </c>
       <c r="L5">
-        <v>17.66013450152344</v>
+        <v>6.081110400190727</v>
       </c>
       <c r="M5">
-        <v>9.971380121147527</v>
+        <v>1.628907674523635</v>
       </c>
       <c r="N5">
         <v>100</v>
       </c>
       <c r="O5">
-        <v>59.03538751236583</v>
+        <v>60.73555672144785</v>
       </c>
       <c r="P5">
-        <v>21.60625044903851</v>
+        <v>23.3748375234557</v>
       </c>
       <c r="Q5">
-        <v>3.520935492942432</v>
+        <v>4.544465103583228</v>
       </c>
       <c r="R5">
-        <v>0.5601919139200718</v>
+        <v>0.786911421332993</v>
       </c>
       <c r="S5">
-        <v>0.00698920600149333</v>
+        <v>0.0102812053097187</v>
       </c>
       <c r="T5">
         <v>100</v>
       </c>
       <c r="U5">
-        <v>66.28764919055384</v>
+        <v>65.35963683612806</v>
       </c>
       <c r="V5">
-        <v>42.57708231638868</v>
+        <v>41.17192249129889</v>
       </c>
       <c r="W5">
-        <v>21.3709430801243</v>
+        <v>23.53967943423315</v>
       </c>
       <c r="X5">
-        <v>8.818757381485343</v>
+        <v>9.777791981187757</v>
       </c>
       <c r="Y5">
-        <v>0.5563534275620854</v>
+        <v>0.6247353505250022</v>
       </c>
     </row>
     <row r="6" spans="1:25">
@@ -908,73 +926,73 @@
         <v>100</v>
       </c>
       <c r="C6">
-        <v>97.08071708174958</v>
+        <v>99.61733143574618</v>
       </c>
       <c r="D6">
-        <v>94.26408350825439</v>
+        <v>99.21929569621042</v>
       </c>
       <c r="E6">
-        <v>91.58459181936801</v>
+        <v>98.69935854376405</v>
       </c>
       <c r="F6">
-        <v>90.78353094684292</v>
+        <v>98.66634255000021</v>
       </c>
       <c r="G6">
-        <v>90.75787144721167</v>
+        <v>98.63954865890871</v>
       </c>
       <c r="H6">
         <v>100</v>
       </c>
       <c r="I6">
-        <v>63.9229067770905</v>
+        <v>50.41963123863514</v>
       </c>
       <c r="J6">
-        <v>39.93970005988486</v>
+        <v>25.4086188313229</v>
       </c>
       <c r="K6">
-        <v>25.84304928639227</v>
+        <v>16.45881412865258</v>
       </c>
       <c r="L6">
-        <v>16.15661327358997</v>
+        <v>8.188443037126177</v>
       </c>
       <c r="M6">
-        <v>11.30382416795916</v>
+        <v>3.222028219426738</v>
       </c>
       <c r="N6">
         <v>100</v>
       </c>
       <c r="O6">
-        <v>74.17841317948115</v>
+        <v>76.86303066952948</v>
       </c>
       <c r="P6">
-        <v>49.49022855982458</v>
+        <v>54.27786445996389</v>
       </c>
       <c r="Q6">
-        <v>32.16976813473167</v>
+        <v>36.47793119306553</v>
       </c>
       <c r="R6">
-        <v>23.15084910130469</v>
+        <v>26.86390342193958</v>
       </c>
       <c r="S6">
-        <v>20.47051528113071</v>
+        <v>23.90676400428615</v>
       </c>
       <c r="T6">
         <v>100</v>
       </c>
       <c r="U6">
-        <v>93.8566359360982</v>
+        <v>95.93178191527458</v>
       </c>
       <c r="V6">
-        <v>90.22960417484221</v>
+        <v>92.56888002691697</v>
       </c>
       <c r="W6">
-        <v>86.89870191877442</v>
+        <v>89.21277741012054</v>
       </c>
       <c r="X6">
-        <v>83.9327339430528</v>
+        <v>86.20175692413177</v>
       </c>
       <c r="Y6">
-        <v>81.90906043986963</v>
+        <v>84.14062268722108</v>
       </c>
     </row>
     <row r="7" spans="1:25">
@@ -985,73 +1003,73 @@
         <v>100</v>
       </c>
       <c r="C7">
-        <v>99.41525178456814</v>
+        <v>99.99280816363326</v>
       </c>
       <c r="D7">
-        <v>98.85243423654693</v>
+        <v>99.95176725020012</v>
       </c>
       <c r="E7">
-        <v>98.31958409827689</v>
+        <v>99.84236643380183</v>
       </c>
       <c r="F7">
-        <v>98.17973004650014</v>
+        <v>99.78494411531111</v>
       </c>
       <c r="G7">
-        <v>98.16506253125826</v>
+        <v>99.76039073646527</v>
       </c>
       <c r="H7">
         <v>100</v>
       </c>
       <c r="I7">
-        <v>64.57348171294228</v>
+        <v>60.89431410642364</v>
       </c>
       <c r="J7">
-        <v>42.8841833157591</v>
+        <v>29.55941288745796</v>
       </c>
       <c r="K7">
-        <v>28.48425427168896</v>
+        <v>15.4717800952286</v>
       </c>
       <c r="L7">
-        <v>17.65969172991384</v>
+        <v>6.081110400190727</v>
       </c>
       <c r="M7">
-        <v>9.971130120558582</v>
+        <v>1.628907674523635</v>
       </c>
       <c r="N7">
         <v>100</v>
       </c>
       <c r="O7">
-        <v>69.64495730342911</v>
+        <v>70.9496677575665</v>
       </c>
       <c r="P7">
-        <v>41.48096287286857</v>
+        <v>43.54184583043826</v>
       </c>
       <c r="Q7">
-        <v>21.63458674092214</v>
+        <v>24.14448580748757</v>
       </c>
       <c r="R7">
-        <v>13.13446451352029</v>
+        <v>15.55094838164174</v>
       </c>
       <c r="S7">
-        <v>11.08100666404445</v>
+        <v>13.19635112823015</v>
       </c>
       <c r="T7">
         <v>100</v>
       </c>
       <c r="U7">
-        <v>92.58211146928646</v>
+        <v>94.10337725749957</v>
       </c>
       <c r="V7">
-        <v>84.24655237974736</v>
+        <v>89.20775652040867</v>
       </c>
       <c r="W7">
-        <v>79.08357579039593</v>
+        <v>84.39375206419986</v>
       </c>
       <c r="X7">
-        <v>74.381135819542</v>
+        <v>80.18714155289129</v>
       </c>
       <c r="Y7">
-        <v>70.78245002184174</v>
+        <v>77.29258831613164</v>
       </c>
     </row>
     <row r="8" spans="1:25">
@@ -1062,37 +1080,37 @@
         <v>100</v>
       </c>
       <c r="C8">
-        <v>68.2670316274659</v>
+        <v>69.86888238204503</v>
       </c>
       <c r="D8">
-        <v>37.84268362308156</v>
+        <v>34.35300730281398</v>
       </c>
       <c r="E8">
-        <v>8.048035532940494</v>
+        <v>11.63360707587902</v>
       </c>
       <c r="F8">
-        <v>0.8576987972351761</v>
+        <v>4.982902920391894</v>
       </c>
       <c r="G8">
-        <v>0.5290487265198803</v>
+        <v>4.078118625030664</v>
       </c>
       <c r="H8">
         <v>100</v>
       </c>
       <c r="I8">
-        <v>52.26967527957643</v>
+        <v>67.45543810543829</v>
       </c>
       <c r="J8">
-        <v>36.54743874766725</v>
+        <v>43.79122804026746</v>
       </c>
       <c r="K8">
-        <v>27.00165214294803</v>
+        <v>24.65150346231158</v>
       </c>
       <c r="L8">
-        <v>19.72090597033521</v>
+        <v>6.471441521355374</v>
       </c>
       <c r="M8">
-        <v>13.39896159535288</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:25">
@@ -1103,37 +1121,37 @@
         <v>100</v>
       </c>
       <c r="C9">
-        <v>68.22034253094473</v>
+        <v>74.94808017193937</v>
       </c>
       <c r="D9">
-        <v>38.30574214435755</v>
+        <v>43.68497880011775</v>
       </c>
       <c r="E9">
-        <v>9.383507714160283</v>
+        <v>14.42520887917621</v>
       </c>
       <c r="F9">
-        <v>2.042658541992902</v>
+        <v>6.443646617434914</v>
       </c>
       <c r="G9">
-        <v>1.484162183203121</v>
+        <v>4.335892362260187</v>
       </c>
       <c r="H9">
         <v>100</v>
       </c>
       <c r="I9">
-        <v>45.70170853761678</v>
+        <v>53.51074399507135</v>
       </c>
       <c r="J9">
-        <v>25.99130231005933</v>
+        <v>24.56657766399224</v>
       </c>
       <c r="K9">
-        <v>15.96374244826046</v>
+        <v>8.154957539847988</v>
       </c>
       <c r="L9">
-        <v>10.18210877776742</v>
+        <v>2.128570620548525</v>
       </c>
       <c r="M9">
-        <v>6.218497099543092</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:25">
@@ -1144,37 +1162,37 @@
         <v>100</v>
       </c>
       <c r="C10">
-        <v>68.45613376373582</v>
+        <v>90.47617302960077</v>
       </c>
       <c r="D10">
-        <v>38.20225348925477</v>
+        <v>39.41640319989995</v>
       </c>
       <c r="E10">
-        <v>8.479071178483782</v>
+        <v>13.07373837196427</v>
       </c>
       <c r="F10">
-        <v>0.871082945915571</v>
+        <v>7.690310773543637</v>
       </c>
       <c r="G10">
-        <v>0.6119943134626324</v>
+        <v>6.1468156344892</v>
       </c>
       <c r="H10">
         <v>100</v>
       </c>
       <c r="I10">
-        <v>67.45768830005026</v>
+        <v>71.94511009160691</v>
       </c>
       <c r="J10">
-        <v>40.52636604696601</v>
+        <v>46.49772096268912</v>
       </c>
       <c r="K10">
-        <v>20.76225593843358</v>
+        <v>22.96945941531929</v>
       </c>
       <c r="L10">
-        <v>6.291282042672146</v>
+        <v>8.901622793342538</v>
       </c>
       <c r="M10">
-        <v>1.738313324316072</v>
+        <v>2.459563790773982</v>
       </c>
     </row>
     <row r="11" spans="1:25">
@@ -1185,37 +1203,37 @@
         <v>100</v>
       </c>
       <c r="C11">
-        <v>68.24478501412364</v>
+        <v>81.45442693131186</v>
       </c>
       <c r="D11">
-        <v>38.51679296702105</v>
+        <v>42.16778580711952</v>
       </c>
       <c r="E11">
-        <v>9.880617964722044</v>
+        <v>16.1575414468421</v>
       </c>
       <c r="F11">
-        <v>2.278313223142147</v>
+        <v>8.217624977941245</v>
       </c>
       <c r="G11">
-        <v>1.618561412955744</v>
+        <v>5.96128616921553</v>
       </c>
       <c r="H11">
         <v>100</v>
       </c>
       <c r="I11">
-        <v>45.412742702361</v>
+        <v>64.88103555652009</v>
       </c>
       <c r="J11">
-        <v>21.88228547157853</v>
+        <v>39.06217677577181</v>
       </c>
       <c r="K11">
-        <v>8.81655728846278</v>
+        <v>16.3134520439698</v>
       </c>
       <c r="L11">
-        <v>1.759423140537855</v>
+        <v>3.249778869186669</v>
       </c>
       <c r="M11">
-        <v>0.2338607476372556</v>
+        <v>0.7332969546046652</v>
       </c>
     </row>
     <row r="12" spans="1:25">
@@ -1226,37 +1244,37 @@
         <v>100</v>
       </c>
       <c r="C12">
-        <v>68.45613376373582</v>
+        <v>70.89807098910654</v>
       </c>
       <c r="D12">
-        <v>38.20225348925477</v>
+        <v>34.35300730281398</v>
       </c>
       <c r="E12">
-        <v>8.479071178483782</v>
+        <v>11.63360707587902</v>
       </c>
       <c r="F12">
-        <v>0.871082945915571</v>
+        <v>6.026207573706807</v>
       </c>
       <c r="G12">
-        <v>0.6119943134626324</v>
+        <v>4.816708715878014</v>
       </c>
       <c r="H12">
         <v>100</v>
       </c>
       <c r="I12">
-        <v>67.45768830005026</v>
+        <v>71.94511009160691</v>
       </c>
       <c r="J12">
-        <v>40.52636604696601</v>
+        <v>46.49772096268912</v>
       </c>
       <c r="K12">
-        <v>25.65247479766251</v>
+        <v>22.96945941531929</v>
       </c>
       <c r="L12">
-        <v>18.73552183817828</v>
+        <v>8.901622793342538</v>
       </c>
       <c r="M12">
-        <v>12.72946273139088</v>
+        <v>2.459563790773982</v>
       </c>
     </row>
     <row r="13" spans="1:25">
@@ -1267,37 +1285,37 @@
         <v>100</v>
       </c>
       <c r="C13">
-        <v>68.23266213368075</v>
+        <v>78.16796543013426</v>
       </c>
       <c r="D13">
-        <v>38.41205608389068</v>
+        <v>42.93414817840256</v>
       </c>
       <c r="E13">
-        <v>9.633910603176869</v>
+        <v>15.28251251220513</v>
       </c>
       <c r="F13">
-        <v>2.161361583311725</v>
+        <v>7.321558505771303</v>
       </c>
       <c r="G13">
-        <v>1.551861324976318</v>
+        <v>5.140272688379194</v>
       </c>
       <c r="H13">
         <v>100</v>
       </c>
       <c r="I13">
-        <v>45.60941128922716</v>
+        <v>60.67029301801937</v>
       </c>
       <c r="J13">
-        <v>24.67884277516628</v>
+        <v>33.69404943236664</v>
       </c>
       <c r="K13">
-        <v>13.68086188967295</v>
+        <v>13.29213237787906</v>
       </c>
       <c r="L13">
-        <v>7.491820136812126</v>
+        <v>2.834563899642181</v>
       </c>
       <c r="M13">
-        <v>4.306945695450507</v>
+        <v>0.4617365418490378</v>
       </c>
     </row>
     <row r="14" spans="1:25">
@@ -1422,42 +1440,6 @@
       <c r="M16">
         <v>41.70809805245049</v>
       </c>
-      <c r="N16">
-        <v>100</v>
-      </c>
-      <c r="O16">
-        <v>68.42075839541103</v>
-      </c>
-      <c r="P16">
-        <v>37.34071980271996</v>
-      </c>
-      <c r="Q16">
-        <v>13.69820579728939</v>
-      </c>
-      <c r="R16">
-        <v>2.932508385157989</v>
-      </c>
-      <c r="S16">
-        <v>0</v>
-      </c>
-      <c r="T16">
-        <v>100</v>
-      </c>
-      <c r="U16">
-        <v>72.59486009052286</v>
-      </c>
-      <c r="V16">
-        <v>50.40249516157637</v>
-      </c>
-      <c r="W16">
-        <v>29.42995273380574</v>
-      </c>
-      <c r="X16">
-        <v>10.78563662860183</v>
-      </c>
-      <c r="Y16">
-        <v>0</v>
-      </c>
     </row>
     <row r="17" spans="1:25">
       <c r="A17" s="1" t="s">
@@ -1499,42 +1481,6 @@
       <c r="M17">
         <v>23.58484698134584</v>
       </c>
-      <c r="N17">
-        <v>100</v>
-      </c>
-      <c r="O17">
-        <v>67.37733532364706</v>
-      </c>
-      <c r="P17">
-        <v>35.77658450336362</v>
-      </c>
-      <c r="Q17">
-        <v>11.15990775762401</v>
-      </c>
-      <c r="R17">
-        <v>0.9210604732360059</v>
-      </c>
-      <c r="S17">
-        <v>0</v>
-      </c>
-      <c r="T17">
-        <v>100</v>
-      </c>
-      <c r="U17">
-        <v>53.9248635276161</v>
-      </c>
-      <c r="V17">
-        <v>26.53893891616757</v>
-      </c>
-      <c r="W17">
-        <v>11.22466432366339</v>
-      </c>
-      <c r="X17">
-        <v>2.758633228018589</v>
-      </c>
-      <c r="Y17">
-        <v>0</v>
-      </c>
     </row>
     <row r="18" spans="1:25">
       <c r="A18" s="1" t="s">
@@ -1544,70 +1490,70 @@
         <v>100</v>
       </c>
       <c r="C18">
-        <v>60.7229157361331</v>
+        <v>84.66096178766146</v>
       </c>
       <c r="D18">
-        <v>27.97555158809081</v>
+        <v>66.03151285455611</v>
       </c>
       <c r="E18">
-        <v>15.25931360814973</v>
+        <v>13.66990659736944</v>
       </c>
       <c r="F18">
-        <v>4.593768393794482</v>
+        <v>9.470391094072115</v>
       </c>
       <c r="G18">
-        <v>0</v>
+        <v>7.828078647443387</v>
       </c>
       <c r="H18">
         <v>100</v>
       </c>
       <c r="I18">
-        <v>70.48084578667711</v>
+        <v>73.10039839981562</v>
       </c>
       <c r="J18">
-        <v>43.00011617541635</v>
+        <v>57.43285234512619</v>
       </c>
       <c r="K18">
-        <v>0</v>
+        <v>51.18048581729582</v>
       </c>
       <c r="L18">
-        <v>0</v>
+        <v>45.34051248703555</v>
       </c>
       <c r="M18">
-        <v>0</v>
+        <v>41.70809805245049</v>
       </c>
       <c r="N18">
         <v>100</v>
       </c>
       <c r="O18">
-        <v>57.78763288986668</v>
+        <v>68.97617549059841</v>
       </c>
       <c r="P18">
-        <v>18.78020794817624</v>
+        <v>38.2959399778436</v>
       </c>
       <c r="Q18">
-        <v>0</v>
+        <v>14.75627959591148</v>
       </c>
       <c r="R18">
-        <v>0</v>
+        <v>3.349029222208283</v>
       </c>
       <c r="S18">
         <v>0</v>
       </c>
       <c r="T18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U18">
-        <v>0</v>
+        <v>74.14116356372091</v>
       </c>
       <c r="V18">
-        <v>0</v>
+        <v>52.32188763897759</v>
       </c>
       <c r="W18">
-        <v>0</v>
+        <v>30.70319791717836</v>
       </c>
       <c r="X18">
-        <v>0</v>
+        <v>11.31961159961356</v>
       </c>
       <c r="Y18">
         <v>0</v>
@@ -1621,70 +1567,70 @@
         <v>100</v>
       </c>
       <c r="C19">
-        <v>78.43526195351055</v>
+        <v>72.1627398323843</v>
       </c>
       <c r="D19">
-        <v>50.96690713157989</v>
+        <v>39.40471865608478</v>
       </c>
       <c r="E19">
-        <v>16.32535488543899</v>
+        <v>17.84974312712461</v>
       </c>
       <c r="F19">
-        <v>0.3804916538860575</v>
+        <v>9.671437730495363</v>
       </c>
       <c r="G19">
-        <v>0</v>
+        <v>5.452664126060338</v>
       </c>
       <c r="H19">
         <v>100</v>
       </c>
       <c r="I19">
-        <v>13.23740358050935</v>
+        <v>77.77233891835158</v>
       </c>
       <c r="J19">
-        <v>6.416002550584768</v>
+        <v>60.9700014548528</v>
       </c>
       <c r="K19">
-        <v>0</v>
+        <v>45.1182084137255</v>
       </c>
       <c r="L19">
-        <v>0</v>
+        <v>30.81766028927323</v>
       </c>
       <c r="M19">
-        <v>0</v>
+        <v>22.95620243583926</v>
       </c>
       <c r="N19">
         <v>100</v>
       </c>
       <c r="O19">
-        <v>49.06753113552977</v>
+        <v>67.91257038327615</v>
       </c>
       <c r="P19">
-        <v>4.324702749845449</v>
+        <v>36.23383333187582</v>
       </c>
       <c r="Q19">
-        <v>0</v>
+        <v>11.64108741112052</v>
       </c>
       <c r="R19">
-        <v>0</v>
+        <v>1.018388408421855</v>
       </c>
       <c r="S19">
         <v>0</v>
       </c>
       <c r="T19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U19">
-        <v>0</v>
+        <v>55.0246899260751</v>
       </c>
       <c r="V19">
-        <v>0</v>
+        <v>28.49847784573537</v>
       </c>
       <c r="W19">
-        <v>0</v>
+        <v>12.57796378411592</v>
       </c>
       <c r="X19">
-        <v>0</v>
+        <v>3.094169792924138</v>
       </c>
       <c r="Y19">
         <v>0</v>
@@ -1698,19 +1644,19 @@
         <v>100</v>
       </c>
       <c r="C20">
-        <v>71.97868500896098</v>
+        <v>60.7229157361331</v>
       </c>
       <c r="D20">
-        <v>45.99677476233726</v>
+        <v>27.97555158809081</v>
       </c>
       <c r="E20">
-        <v>10.26805472841607</v>
+        <v>15.25931360814973</v>
       </c>
       <c r="F20">
-        <v>3.09116559816672</v>
+        <v>4.593768393794482</v>
       </c>
       <c r="G20">
-        <v>2.282996569953399</v>
+        <v>0</v>
       </c>
       <c r="H20">
         <v>100</v>
@@ -1722,48 +1668,12 @@
         <v>43.00011617541635</v>
       </c>
       <c r="K20">
-        <v>18.43305488908583</v>
+        <v>0</v>
       </c>
       <c r="L20">
-        <v>16.32974251859038</v>
+        <v>0</v>
       </c>
       <c r="M20">
-        <v>15.02149986353558</v>
-      </c>
-      <c r="N20">
-        <v>100</v>
-      </c>
-      <c r="O20">
-        <v>68.42075839541103</v>
-      </c>
-      <c r="P20">
-        <v>37.34071980271996</v>
-      </c>
-      <c r="Q20">
-        <v>13.69820579728939</v>
-      </c>
-      <c r="R20">
-        <v>2.932508385157989</v>
-      </c>
-      <c r="S20">
-        <v>0</v>
-      </c>
-      <c r="T20">
-        <v>100</v>
-      </c>
-      <c r="U20">
-        <v>72.59486009052286</v>
-      </c>
-      <c r="V20">
-        <v>50.40249516157637</v>
-      </c>
-      <c r="W20">
-        <v>29.42995273380574</v>
-      </c>
-      <c r="X20">
-        <v>10.78563662860183</v>
-      </c>
-      <c r="Y20">
         <v>0</v>
       </c>
     </row>
@@ -1775,72 +1685,36 @@
         <v>100</v>
       </c>
       <c r="C21">
-        <v>77.23932907262585</v>
+        <v>78.43526195351055</v>
       </c>
       <c r="D21">
-        <v>45.09444779932792</v>
+        <v>50.96690713157989</v>
       </c>
       <c r="E21">
-        <v>15.42942584942032</v>
+        <v>16.32535488543899</v>
       </c>
       <c r="F21">
-        <v>3.809430500536067</v>
+        <v>0.3804916538860575</v>
       </c>
       <c r="G21">
-        <v>2.02028083124552</v>
+        <v>0</v>
       </c>
       <c r="H21">
         <v>100</v>
       </c>
       <c r="I21">
-        <v>42.14425218523644</v>
+        <v>13.23740358050935</v>
       </c>
       <c r="J21">
-        <v>31.12484699482849</v>
+        <v>6.416002550584768</v>
       </c>
       <c r="K21">
-        <v>21.04210152546269</v>
+        <v>0</v>
       </c>
       <c r="L21">
-        <v>15.12640561432428</v>
+        <v>0</v>
       </c>
       <c r="M21">
-        <v>11.14456529492854</v>
-      </c>
-      <c r="N21">
-        <v>100</v>
-      </c>
-      <c r="O21">
-        <v>62.55130915276234</v>
-      </c>
-      <c r="P21">
-        <v>27.48660859134573</v>
-      </c>
-      <c r="Q21">
-        <v>8.218417242667662</v>
-      </c>
-      <c r="R21">
-        <v>0.6782904876262205</v>
-      </c>
-      <c r="S21">
-        <v>0</v>
-      </c>
-      <c r="T21">
-        <v>100</v>
-      </c>
-      <c r="U21">
-        <v>53.9248635276161</v>
-      </c>
-      <c r="V21">
-        <v>26.53893891616757</v>
-      </c>
-      <c r="W21">
-        <v>11.22466432366339</v>
-      </c>
-      <c r="X21">
-        <v>2.758633228018589</v>
-      </c>
-      <c r="Y21">
         <v>0</v>
       </c>
     </row>
@@ -1852,37 +1726,73 @@
         <v>100</v>
       </c>
       <c r="C22">
-        <v>93.12654178761444</v>
+        <v>83.6525157609244</v>
       </c>
       <c r="D22">
-        <v>87.29065898306889</v>
+        <v>61.46974407378942</v>
       </c>
       <c r="E22">
-        <v>83.03202550552105</v>
+        <v>28.24810452819843</v>
       </c>
       <c r="F22">
-        <v>80.93872746956058</v>
+        <v>0</v>
       </c>
       <c r="G22">
-        <v>80.01698397463683</v>
+        <v>0</v>
       </c>
       <c r="H22">
         <v>100</v>
       </c>
       <c r="I22">
-        <v>99.00500531683059</v>
+        <v>0</v>
       </c>
       <c r="J22">
-        <v>98.20464837772704</v>
+        <v>0</v>
       </c>
       <c r="K22">
-        <v>97.5707762393108</v>
+        <v>0</v>
       </c>
       <c r="L22">
-        <v>97.12111915131804</v>
+        <v>0</v>
       </c>
       <c r="M22">
-        <v>96.87055256884388</v>
+        <v>0</v>
+      </c>
+      <c r="N22">
+        <v>100</v>
+      </c>
+      <c r="O22">
+        <v>57.03797106382076</v>
+      </c>
+      <c r="P22">
+        <v>11.352903885216</v>
+      </c>
+      <c r="Q22">
+        <v>0</v>
+      </c>
+      <c r="R22">
+        <v>0</v>
+      </c>
+      <c r="S22">
+        <v>0</v>
+      </c>
+      <c r="T22">
+        <v>0</v>
+      </c>
+      <c r="U22">
+        <v>0</v>
+      </c>
+      <c r="V22">
+        <v>0</v>
+      </c>
+      <c r="W22">
+        <v>0</v>
+      </c>
+      <c r="X22">
+        <v>0</v>
+      </c>
+      <c r="Y22">
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:25">
@@ -1893,37 +1803,391 @@
         <v>100</v>
       </c>
       <c r="C23">
-        <v>91.530830337182</v>
+        <v>80.80006765757446</v>
       </c>
       <c r="D23">
-        <v>85.42968163711879</v>
+        <v>53.89164834040142</v>
       </c>
       <c r="E23">
-        <v>81.87477183407282</v>
+        <v>7.870486380498452</v>
       </c>
       <c r="F23">
-        <v>80.64101544569995</v>
+        <v>0</v>
       </c>
       <c r="G23">
-        <v>80.14352906683713</v>
+        <v>0</v>
       </c>
       <c r="H23">
         <v>100</v>
       </c>
       <c r="I23">
-        <v>99.59048818998274</v>
+        <v>0</v>
       </c>
       <c r="J23">
-        <v>99.26513695524228</v>
+        <v>0</v>
       </c>
       <c r="K23">
-        <v>99.00585362585127</v>
+        <v>0</v>
       </c>
       <c r="L23">
-        <v>98.80802740217099</v>
+        <v>0</v>
       </c>
       <c r="M23">
-        <v>98.6953459302986</v>
+        <v>0</v>
+      </c>
+      <c r="N23">
+        <v>100</v>
+      </c>
+      <c r="O23">
+        <v>46.24334053098276</v>
+      </c>
+      <c r="P23">
+        <v>1.323151453004936</v>
+      </c>
+      <c r="Q23">
+        <v>0</v>
+      </c>
+      <c r="R23">
+        <v>0</v>
+      </c>
+      <c r="S23">
+        <v>0</v>
+      </c>
+      <c r="T23">
+        <v>0</v>
+      </c>
+      <c r="U23">
+        <v>0</v>
+      </c>
+      <c r="V23">
+        <v>0</v>
+      </c>
+      <c r="W23">
+        <v>0</v>
+      </c>
+      <c r="X23">
+        <v>0</v>
+      </c>
+      <c r="Y23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:25">
+      <c r="A24" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B24">
+        <v>100</v>
+      </c>
+      <c r="C24">
+        <v>71.97868500896098</v>
+      </c>
+      <c r="D24">
+        <v>45.99677476233726</v>
+      </c>
+      <c r="E24">
+        <v>10.26805472841607</v>
+      </c>
+      <c r="F24">
+        <v>3.09116559816672</v>
+      </c>
+      <c r="G24">
+        <v>2.282996569953399</v>
+      </c>
+      <c r="H24">
+        <v>100</v>
+      </c>
+      <c r="I24">
+        <v>70.48084578667711</v>
+      </c>
+      <c r="J24">
+        <v>43.00011617541635</v>
+      </c>
+      <c r="K24">
+        <v>18.43305488908583</v>
+      </c>
+      <c r="L24">
+        <v>16.32974251859038</v>
+      </c>
+      <c r="M24">
+        <v>15.02149986353558</v>
+      </c>
+    </row>
+    <row r="25" spans="1:25">
+      <c r="A25" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B25">
+        <v>100</v>
+      </c>
+      <c r="C25">
+        <v>77.23932907262585</v>
+      </c>
+      <c r="D25">
+        <v>45.09444779932792</v>
+      </c>
+      <c r="E25">
+        <v>15.42942584942032</v>
+      </c>
+      <c r="F25">
+        <v>3.809430500536067</v>
+      </c>
+      <c r="G25">
+        <v>2.02028083124552</v>
+      </c>
+      <c r="H25">
+        <v>100</v>
+      </c>
+      <c r="I25">
+        <v>42.14425218523644</v>
+      </c>
+      <c r="J25">
+        <v>31.12484699482849</v>
+      </c>
+      <c r="K25">
+        <v>21.04210152546269</v>
+      </c>
+      <c r="L25">
+        <v>15.12640561432428</v>
+      </c>
+      <c r="M25">
+        <v>11.14456529492854</v>
+      </c>
+    </row>
+    <row r="26" spans="1:25">
+      <c r="A26" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B26">
+        <v>100</v>
+      </c>
+      <c r="C26">
+        <v>83.6525157609244</v>
+      </c>
+      <c r="D26">
+        <v>62.88265890442231</v>
+      </c>
+      <c r="E26">
+        <v>28.24810452819843</v>
+      </c>
+      <c r="F26">
+        <v>9.018775234966091</v>
+      </c>
+      <c r="G26">
+        <v>7.454779970715292</v>
+      </c>
+      <c r="H26">
+        <v>100</v>
+      </c>
+      <c r="I26">
+        <v>27.95351114701213</v>
+      </c>
+      <c r="J26">
+        <v>21.96225893945656</v>
+      </c>
+      <c r="K26">
+        <v>19.57136092444174</v>
+      </c>
+      <c r="L26">
+        <v>17.33816161008485</v>
+      </c>
+      <c r="M26">
+        <v>15.94913036524286</v>
+      </c>
+      <c r="N26">
+        <v>100</v>
+      </c>
+      <c r="O26">
+        <v>68.97617549059841</v>
+      </c>
+      <c r="P26">
+        <v>38.2959399778436</v>
+      </c>
+      <c r="Q26">
+        <v>14.75627959591148</v>
+      </c>
+      <c r="R26">
+        <v>3.349029222208283</v>
+      </c>
+      <c r="S26">
+        <v>0</v>
+      </c>
+      <c r="T26">
+        <v>100</v>
+      </c>
+      <c r="U26">
+        <v>74.14116356372091</v>
+      </c>
+      <c r="V26">
+        <v>52.32188763897759</v>
+      </c>
+      <c r="W26">
+        <v>30.70319791717836</v>
+      </c>
+      <c r="X26">
+        <v>11.31961159961356</v>
+      </c>
+      <c r="Y26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:25">
+      <c r="A27" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B27">
+        <v>100</v>
+      </c>
+      <c r="C27">
+        <v>76.89264512109905</v>
+      </c>
+      <c r="D27">
+        <v>47.33791130537778</v>
+      </c>
+      <c r="E27">
+        <v>12.3849948461953</v>
+      </c>
+      <c r="F27">
+        <v>4.375253911973426</v>
+      </c>
+      <c r="G27">
+        <v>2.466726324773714</v>
+      </c>
+      <c r="H27">
+        <v>100</v>
+      </c>
+      <c r="I27">
+        <v>45.67947223590767</v>
+      </c>
+      <c r="J27">
+        <v>35.81064331373756</v>
+      </c>
+      <c r="K27">
+        <v>26.50011530105018</v>
+      </c>
+      <c r="L27">
+        <v>18.10070877561474</v>
+      </c>
+      <c r="M27">
+        <v>13.48329272841704</v>
+      </c>
+      <c r="N27">
+        <v>100</v>
+      </c>
+      <c r="O27">
+        <v>63.78258370227793</v>
+      </c>
+      <c r="P27">
+        <v>29.58012509340412</v>
+      </c>
+      <c r="Q27">
+        <v>9.422385425267274</v>
+      </c>
+      <c r="R27">
+        <v>0.8242913877279776</v>
+      </c>
+      <c r="S27">
+        <v>0</v>
+      </c>
+      <c r="T27">
+        <v>100</v>
+      </c>
+      <c r="U27">
+        <v>55.0246899260751</v>
+      </c>
+      <c r="V27">
+        <v>28.49847784573537</v>
+      </c>
+      <c r="W27">
+        <v>12.57796378411592</v>
+      </c>
+      <c r="X27">
+        <v>3.094169792924138</v>
+      </c>
+      <c r="Y27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:25">
+      <c r="A28" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B28">
+        <v>100</v>
+      </c>
+      <c r="C28">
+        <v>94.55101751526121</v>
+      </c>
+      <c r="D28">
+        <v>90.02158179198781</v>
+      </c>
+      <c r="E28">
+        <v>86.86141349473213</v>
+      </c>
+      <c r="F28">
+        <v>85.18699561744928</v>
+      </c>
+      <c r="G28">
+        <v>84.24580280712712</v>
+      </c>
+      <c r="H28">
+        <v>100</v>
+      </c>
+      <c r="I28">
+        <v>99.05271409813115</v>
+      </c>
+      <c r="J28">
+        <v>98.27223165727914</v>
+      </c>
+      <c r="K28">
+        <v>97.64169894270664</v>
+      </c>
+      <c r="L28">
+        <v>97.19171500586108</v>
+      </c>
+      <c r="M28">
+        <v>96.94096629037439</v>
+      </c>
+    </row>
+    <row r="29" spans="1:25">
+      <c r="A29" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B29">
+        <v>100</v>
+      </c>
+      <c r="C29">
+        <v>95.73785255416001</v>
+      </c>
+      <c r="D29">
+        <v>92.15208186802127</v>
+      </c>
+      <c r="E29">
+        <v>89.59661159182109</v>
+      </c>
+      <c r="F29">
+        <v>88.50931880011608</v>
+      </c>
+      <c r="G29">
+        <v>87.9904806411499</v>
+      </c>
+      <c r="H29">
+        <v>100</v>
+      </c>
+      <c r="I29">
+        <v>99.63699306081617</v>
+      </c>
+      <c r="J29">
+        <v>99.32867258344457</v>
+      </c>
+      <c r="K29">
+        <v>99.07399300212958</v>
+      </c>
+      <c r="L29">
+        <v>98.87619219792087</v>
+      </c>
+      <c r="M29">
+        <v>98.76343299036529</v>
       </c>
     </row>
   </sheetData>

--- a/verification/model_verification_results_118_buses.xlsx
+++ b/verification/model_verification_results_118_buses.xlsx
@@ -615,22 +615,22 @@
         <v>25</v>
       </c>
       <c r="B2">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="C2">
-        <v>99.61733143574618</v>
+        <v>0</v>
       </c>
       <c r="D2">
-        <v>99.21929569621042</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>98.68718566896206</v>
+        <v>0</v>
       </c>
       <c r="F2">
-        <v>98.66272892049972</v>
+        <v>0</v>
       </c>
       <c r="G2">
-        <v>98.63954865890871</v>
+        <v>0</v>
       </c>
       <c r="H2">
         <v>0</v>
@@ -654,37 +654,37 @@
         <v>100</v>
       </c>
       <c r="O2">
-        <v>76.86303066952948</v>
+        <v>69.26706084058965</v>
       </c>
       <c r="P2">
-        <v>54.27786445996389</v>
+        <v>39.24659477394601</v>
       </c>
       <c r="Q2">
-        <v>36.47793119306553</v>
+        <v>15.80490402484343</v>
       </c>
       <c r="R2">
-        <v>26.86390342193958</v>
+        <v>3.449395272589166</v>
       </c>
       <c r="S2">
-        <v>23.90676400428615</v>
+        <v>0.002921035616739516</v>
       </c>
       <c r="T2">
         <v>100</v>
       </c>
       <c r="U2">
-        <v>95.93178191527458</v>
+        <v>74.68645839982085</v>
       </c>
       <c r="V2">
-        <v>92.56888002691697</v>
+        <v>52.27781269687066</v>
       </c>
       <c r="W2">
-        <v>89.21277741012054</v>
+        <v>29.82203523378543</v>
       </c>
       <c r="X2">
-        <v>86.20175692413177</v>
+        <v>13.14536163258359</v>
       </c>
       <c r="Y2">
-        <v>84.14062268722108</v>
+        <v>2.308554720983226</v>
       </c>
     </row>
     <row r="3" spans="1:25">
@@ -692,22 +692,22 @@
         <v>26</v>
       </c>
       <c r="B3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="C3">
-        <v>99.99509658663789</v>
+        <v>0</v>
       </c>
       <c r="D3">
-        <v>99.91764012314678</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>99.78444320368817</v>
+        <v>0</v>
       </c>
       <c r="F3">
-        <v>99.73630116690009</v>
+        <v>0</v>
       </c>
       <c r="G3">
-        <v>99.71225198304393</v>
+        <v>0</v>
       </c>
       <c r="H3">
         <v>0</v>
@@ -731,37 +731,37 @@
         <v>100</v>
       </c>
       <c r="O3">
-        <v>71.19148824739194</v>
+        <v>65.30585806431029</v>
       </c>
       <c r="P3">
-        <v>44.01931339549556</v>
+        <v>35.90818541718734</v>
       </c>
       <c r="Q3">
-        <v>24.60854116182523</v>
+        <v>13.25754375668016</v>
       </c>
       <c r="R3">
-        <v>15.90050217245484</v>
+        <v>2.711238937861925</v>
       </c>
       <c r="S3">
-        <v>13.50854579478409</v>
+        <v>0.0004804361875524899</v>
       </c>
       <c r="T3">
         <v>100</v>
       </c>
       <c r="U3">
-        <v>94.16991656064667</v>
+        <v>73.05017201115135</v>
       </c>
       <c r="V3">
-        <v>89.31895896217742</v>
+        <v>49.76680865316388</v>
       </c>
       <c r="W3">
-        <v>84.53463920402312</v>
+        <v>26.64233093657431</v>
       </c>
       <c r="X3">
-        <v>80.35014662634673</v>
+        <v>7.80156921827703</v>
       </c>
       <c r="Y3">
-        <v>77.47008688558064</v>
+        <v>0.4645636119839394</v>
       </c>
     </row>
     <row r="4" spans="1:25">
@@ -772,19 +772,19 @@
         <v>100</v>
       </c>
       <c r="C4">
-        <v>99.92495980901941</v>
+        <v>62.5068514368935</v>
       </c>
       <c r="D4">
-        <v>99.92398801175949</v>
+        <v>31.15373477407717</v>
       </c>
       <c r="E4">
-        <v>99.7055641186537</v>
+        <v>7.29017119253979</v>
       </c>
       <c r="F4">
-        <v>99.67221153833576</v>
+        <v>0.9567145058520407</v>
       </c>
       <c r="G4">
-        <v>99.64383007477046</v>
+        <v>0</v>
       </c>
       <c r="H4">
         <v>100</v>
@@ -849,19 +849,19 @@
         <v>100</v>
       </c>
       <c r="C5">
-        <v>99.99051020961504</v>
+        <v>64.5479728537253</v>
       </c>
       <c r="D5">
-        <v>99.98594961252417</v>
+        <v>31.28966379701092</v>
       </c>
       <c r="E5">
-        <v>99.90036032465454</v>
+        <v>5.913429168639507</v>
       </c>
       <c r="F5">
-        <v>99.8336569066557</v>
+        <v>0.382562050182823</v>
       </c>
       <c r="G5">
-        <v>99.80857987004921</v>
+        <v>0</v>
       </c>
       <c r="H5">
         <v>100</v>
@@ -885,37 +885,37 @@
         <v>100</v>
       </c>
       <c r="O5">
-        <v>60.73555672144785</v>
+        <v>60.73555835241289</v>
       </c>
       <c r="P5">
-        <v>23.3748375234557</v>
+        <v>23.37483607916846</v>
       </c>
       <c r="Q5">
-        <v>4.544465103583228</v>
+        <v>4.544465269266794</v>
       </c>
       <c r="R5">
-        <v>0.786911421332993</v>
+        <v>0.7869113907376278</v>
       </c>
       <c r="S5">
-        <v>0.0102812053097187</v>
+        <v>0.01028120552860868</v>
       </c>
       <c r="T5">
         <v>100</v>
       </c>
       <c r="U5">
-        <v>65.35963683612806</v>
+        <v>65.35963661023841</v>
       </c>
       <c r="V5">
-        <v>41.17192249129889</v>
+        <v>41.17192327476221</v>
       </c>
       <c r="W5">
-        <v>23.53967943423315</v>
+        <v>23.53967704544396</v>
       </c>
       <c r="X5">
-        <v>9.777791981187757</v>
+        <v>9.777791673980801</v>
       </c>
       <c r="Y5">
-        <v>0.6247353505250022</v>
+        <v>0.6247353068683611</v>
       </c>
     </row>
     <row r="6" spans="1:25">
@@ -926,19 +926,19 @@
         <v>100</v>
       </c>
       <c r="C6">
-        <v>99.61733143574618</v>
+        <v>62.5068514368935</v>
       </c>
       <c r="D6">
-        <v>99.21929569621042</v>
+        <v>31.15373477407717</v>
       </c>
       <c r="E6">
-        <v>98.69935854376405</v>
+        <v>7.29017119253979</v>
       </c>
       <c r="F6">
-        <v>98.66634255000021</v>
+        <v>0.9567145058520407</v>
       </c>
       <c r="G6">
-        <v>98.63954865890871</v>
+        <v>0.04716008955792296</v>
       </c>
       <c r="H6">
         <v>100</v>
@@ -962,37 +962,37 @@
         <v>100</v>
       </c>
       <c r="O6">
-        <v>76.86303066952948</v>
+        <v>69.26706084058965</v>
       </c>
       <c r="P6">
-        <v>54.27786445996389</v>
+        <v>39.24659477394601</v>
       </c>
       <c r="Q6">
-        <v>36.47793119306553</v>
+        <v>15.80490402484343</v>
       </c>
       <c r="R6">
-        <v>26.86390342193958</v>
+        <v>3.449395272589166</v>
       </c>
       <c r="S6">
-        <v>23.90676400428615</v>
+        <v>0.02028168561058326</v>
       </c>
       <c r="T6">
         <v>100</v>
       </c>
       <c r="U6">
-        <v>95.93178191527458</v>
+        <v>74.68645839982085</v>
       </c>
       <c r="V6">
-        <v>92.56888002691697</v>
+        <v>52.27781269687066</v>
       </c>
       <c r="W6">
-        <v>89.21277741012054</v>
+        <v>29.82203523378543</v>
       </c>
       <c r="X6">
-        <v>86.20175692413177</v>
+        <v>13.14536163258359</v>
       </c>
       <c r="Y6">
-        <v>84.14062268722108</v>
+        <v>2.308554720983226</v>
       </c>
     </row>
     <row r="7" spans="1:25">
@@ -1003,19 +1003,19 @@
         <v>100</v>
       </c>
       <c r="C7">
-        <v>99.99280816363326</v>
+        <v>64.54797561002727</v>
       </c>
       <c r="D7">
-        <v>99.95176725020012</v>
+        <v>31.2896652516904</v>
       </c>
       <c r="E7">
-        <v>99.84236643380183</v>
+        <v>5.913429194807004</v>
       </c>
       <c r="F7">
-        <v>99.78494411531111</v>
+        <v>0.3825620811797635</v>
       </c>
       <c r="G7">
-        <v>99.76039073646527</v>
+        <v>0.01049474786948632</v>
       </c>
       <c r="H7">
         <v>100</v>
@@ -1039,37 +1039,37 @@
         <v>100</v>
       </c>
       <c r="O7">
-        <v>70.9496677575665</v>
+        <v>63.7471062972106</v>
       </c>
       <c r="P7">
-        <v>43.54184583043826</v>
+        <v>31.63355550324959</v>
       </c>
       <c r="Q7">
-        <v>24.14448580748757</v>
+        <v>10.28585802213208</v>
       </c>
       <c r="R7">
-        <v>15.55094838164174</v>
+        <v>2.054927005588864</v>
       </c>
       <c r="S7">
-        <v>13.19635112823015</v>
+        <v>0.003823091864755014</v>
       </c>
       <c r="T7">
         <v>100</v>
       </c>
       <c r="U7">
-        <v>94.10337725749957</v>
+        <v>71.93035221276767</v>
       </c>
       <c r="V7">
-        <v>89.20775652040867</v>
+        <v>48.51530212940218</v>
       </c>
       <c r="W7">
-        <v>84.39375206419986</v>
+        <v>26.19055107976999</v>
       </c>
       <c r="X7">
-        <v>80.18714155289129</v>
+        <v>8.089327127330977</v>
       </c>
       <c r="Y7">
-        <v>77.29258831613164</v>
+        <v>0.487886173985568</v>
       </c>
     </row>
     <row r="8" spans="1:25">
@@ -1080,19 +1080,19 @@
         <v>100</v>
       </c>
       <c r="C8">
-        <v>69.86888238204503</v>
+        <v>80.28748394328882</v>
       </c>
       <c r="D8">
-        <v>34.35300730281398</v>
+        <v>55.27947050777222</v>
       </c>
       <c r="E8">
-        <v>11.63360707587902</v>
+        <v>16.21552947739813</v>
       </c>
       <c r="F8">
-        <v>4.982902920391894</v>
+        <v>3.709891950459716</v>
       </c>
       <c r="G8">
-        <v>4.078118625030664</v>
+        <v>2.36809905033103</v>
       </c>
       <c r="H8">
         <v>100</v>
@@ -1121,19 +1121,19 @@
         <v>100</v>
       </c>
       <c r="C9">
-        <v>74.94808017193937</v>
+        <v>83.22627675217413</v>
       </c>
       <c r="D9">
-        <v>43.68497880011775</v>
+        <v>55.48294776910711</v>
       </c>
       <c r="E9">
-        <v>14.42520887917621</v>
+        <v>14.43391177957585</v>
       </c>
       <c r="F9">
-        <v>6.443646617434914</v>
+        <v>3.365565325511397</v>
       </c>
       <c r="G9">
-        <v>4.335892362260187</v>
+        <v>1.761744168789781</v>
       </c>
       <c r="H9">
         <v>100</v>
@@ -1162,19 +1162,19 @@
         <v>100</v>
       </c>
       <c r="C10">
-        <v>90.47617302960077</v>
+        <v>34.41041316025149</v>
       </c>
       <c r="D10">
-        <v>39.41640319989995</v>
+        <v>22.12342850680242</v>
       </c>
       <c r="E10">
-        <v>13.07373837196427</v>
+        <v>13.52178201167926</v>
       </c>
       <c r="F10">
-        <v>7.690310773543637</v>
+        <v>8.795548937951619</v>
       </c>
       <c r="G10">
-        <v>6.1468156344892</v>
+        <v>7.718577754415673</v>
       </c>
       <c r="H10">
         <v>100</v>
@@ -1203,19 +1203,19 @@
         <v>100</v>
       </c>
       <c r="C11">
-        <v>81.45442693131186</v>
+        <v>47.47356654433737</v>
       </c>
       <c r="D11">
-        <v>42.16778580711952</v>
+        <v>24.58010249038159</v>
       </c>
       <c r="E11">
-        <v>16.1575414468421</v>
+        <v>15.23958245801</v>
       </c>
       <c r="F11">
-        <v>8.217624977941245</v>
+        <v>8.486831300423532</v>
       </c>
       <c r="G11">
-        <v>5.96128616921553</v>
+        <v>4.789910068626658</v>
       </c>
       <c r="H11">
         <v>100</v>
@@ -1244,19 +1244,19 @@
         <v>100</v>
       </c>
       <c r="C12">
-        <v>70.89807098910654</v>
+        <v>80.28748394328882</v>
       </c>
       <c r="D12">
-        <v>34.35300730281398</v>
+        <v>55.27947050777222</v>
       </c>
       <c r="E12">
-        <v>11.63360707587902</v>
+        <v>16.21552947739813</v>
       </c>
       <c r="F12">
-        <v>6.026207573706807</v>
+        <v>3.977525957490704</v>
       </c>
       <c r="G12">
-        <v>4.816708715878014</v>
+        <v>3.490497703972588</v>
       </c>
       <c r="H12">
         <v>100</v>
@@ -1285,19 +1285,19 @@
         <v>100</v>
       </c>
       <c r="C13">
-        <v>78.16796543013426</v>
+        <v>70.89664219082275</v>
       </c>
       <c r="D13">
-        <v>42.93414817840256</v>
+        <v>44.82582627639648</v>
       </c>
       <c r="E13">
-        <v>15.28251251220513</v>
+        <v>14.71175489146744</v>
       </c>
       <c r="F13">
-        <v>7.321558505771303</v>
+        <v>5.131679167971166</v>
       </c>
       <c r="G13">
-        <v>5.140272688379194</v>
+        <v>2.806033967071901</v>
       </c>
       <c r="H13">
         <v>100</v>
@@ -1526,16 +1526,16 @@
         <v>100</v>
       </c>
       <c r="O18">
-        <v>68.97617549059841</v>
+        <v>69.03050260162679</v>
       </c>
       <c r="P18">
-        <v>38.2959399778436</v>
+        <v>38.49067544196561</v>
       </c>
       <c r="Q18">
-        <v>14.75627959591148</v>
+        <v>14.80593015876909</v>
       </c>
       <c r="R18">
-        <v>3.349029222208283</v>
+        <v>3.205403045223767</v>
       </c>
       <c r="S18">
         <v>0</v>
@@ -1544,16 +1544,16 @@
         <v>100</v>
       </c>
       <c r="U18">
-        <v>74.14116356372091</v>
+        <v>75.4140626010895</v>
       </c>
       <c r="V18">
-        <v>52.32188763897759</v>
+        <v>53.07700270434636</v>
       </c>
       <c r="W18">
-        <v>30.70319791717836</v>
+        <v>30.48794689647141</v>
       </c>
       <c r="X18">
-        <v>11.31961159961356</v>
+        <v>10.7484828487507</v>
       </c>
       <c r="Y18">
         <v>0</v>
@@ -1603,16 +1603,16 @@
         <v>100</v>
       </c>
       <c r="O19">
-        <v>67.91257038327615</v>
+        <v>67.63088424878492</v>
       </c>
       <c r="P19">
-        <v>36.23383333187582</v>
+        <v>35.6972543763476</v>
       </c>
       <c r="Q19">
-        <v>11.64108741112052</v>
+        <v>11.34450559223503</v>
       </c>
       <c r="R19">
-        <v>1.018388408421855</v>
+        <v>1.068905125113604</v>
       </c>
       <c r="S19">
         <v>0</v>
@@ -1621,16 +1621,16 @@
         <v>100</v>
       </c>
       <c r="U19">
-        <v>55.0246899260751</v>
+        <v>59.94226598623844</v>
       </c>
       <c r="V19">
-        <v>28.49847784573537</v>
+        <v>34.1516653001638</v>
       </c>
       <c r="W19">
-        <v>12.57796378411592</v>
+        <v>14.48107917762417</v>
       </c>
       <c r="X19">
-        <v>3.094169792924138</v>
+        <v>2.899084437225155</v>
       </c>
       <c r="Y19">
         <v>0</v>
@@ -1762,13 +1762,13 @@
         <v>100</v>
       </c>
       <c r="O22">
-        <v>57.03797106382076</v>
+        <v>57.20390641405481</v>
       </c>
       <c r="P22">
-        <v>11.352903885216</v>
+        <v>26.69147403470046</v>
       </c>
       <c r="Q22">
-        <v>0</v>
+        <v>0.6701107706373384</v>
       </c>
       <c r="R22">
         <v>0</v>
@@ -1839,13 +1839,13 @@
         <v>100</v>
       </c>
       <c r="O23">
-        <v>46.24334053098276</v>
+        <v>46.65141663443049</v>
       </c>
       <c r="P23">
-        <v>1.323151453004936</v>
+        <v>4.0230520461126</v>
       </c>
       <c r="Q23">
-        <v>0</v>
+        <v>0.0268796508745113</v>
       </c>
       <c r="R23">
         <v>0</v>
@@ -1998,16 +1998,16 @@
         <v>100</v>
       </c>
       <c r="O26">
-        <v>68.97617549059841</v>
+        <v>69.03050260162679</v>
       </c>
       <c r="P26">
-        <v>38.2959399778436</v>
+        <v>38.49067544196561</v>
       </c>
       <c r="Q26">
-        <v>14.75627959591148</v>
+        <v>14.80593015876909</v>
       </c>
       <c r="R26">
-        <v>3.349029222208283</v>
+        <v>3.205403045223767</v>
       </c>
       <c r="S26">
         <v>0</v>
@@ -2016,16 +2016,16 @@
         <v>100</v>
       </c>
       <c r="U26">
-        <v>74.14116356372091</v>
+        <v>75.4140626010895</v>
       </c>
       <c r="V26">
-        <v>52.32188763897759</v>
+        <v>53.07700270434636</v>
       </c>
       <c r="W26">
-        <v>30.70319791717836</v>
+        <v>30.48794689647141</v>
       </c>
       <c r="X26">
-        <v>11.31961159961356</v>
+        <v>10.7484828487507</v>
       </c>
       <c r="Y26">
         <v>0</v>
@@ -2075,16 +2075,16 @@
         <v>100</v>
       </c>
       <c r="O27">
-        <v>63.78258370227793</v>
+        <v>63.85614192547725</v>
       </c>
       <c r="P27">
-        <v>29.58012509340412</v>
+        <v>29.99825266812311</v>
       </c>
       <c r="Q27">
-        <v>9.422385425267274</v>
+        <v>9.308173795186436</v>
       </c>
       <c r="R27">
-        <v>0.8242913877279776</v>
+        <v>0.8765816279981192</v>
       </c>
       <c r="S27">
         <v>0</v>
@@ -2093,16 +2093,16 @@
         <v>100</v>
       </c>
       <c r="U27">
-        <v>55.0246899260751</v>
+        <v>59.94226598623844</v>
       </c>
       <c r="V27">
-        <v>28.49847784573537</v>
+        <v>34.1516653001638</v>
       </c>
       <c r="W27">
-        <v>12.57796378411592</v>
+        <v>14.48107917762417</v>
       </c>
       <c r="X27">
-        <v>3.094169792924138</v>
+        <v>2.899084437225155</v>
       </c>
       <c r="Y27">
         <v>0</v>
